--- a/site/Зависшие_авансы_от_20_дней.xlsx
+++ b/site/Зависшие_авансы_от_20_дней.xlsx
@@ -557,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O99"/>
+  <dimension ref="A1:O117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -572,7 +572,7 @@
     <col width="24" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
     <col width="18" customWidth="1" min="14" max="14"/>
     <col width="40" customWidth="1" min="15" max="15"/>
   </cols>
@@ -587,7 +587,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Всего на контроле: 95 сделок с внесенным авансом без реализации ДКП | Для проверки дилерских центров и актуализации статусов в CRM</t>
+          <t>Всего на контроле: 113 сделок с внесенным авансом без реализации ДКП | Для проверки дилерских центров и актуализации статусов в CRM</t>
         </is>
       </c>
     </row>
@@ -685,7 +685,7 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Вагнер Авто (СПб)</t>
+          <t>Вагнер Авто / Авторитэйл</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -704,7 +704,7 @@
         </is>
       </c>
       <c r="H5" s="6" t="n">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="H6" s="6" t="n">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="I6" s="9" t="inlineStr">
         <is>
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="H7" s="6" t="n">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         </is>
       </c>
       <c r="H8" s="6" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="I8" s="9" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="H9" s="6" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         </is>
       </c>
       <c r="H10" s="6" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="I10" s="9" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         </is>
       </c>
       <c r="H11" s="6" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>Вагнер Авто (СПб)</t>
+          <t>Вагнер Авто / Авторитэйл</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="H12" s="6" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="I12" s="9" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         </is>
       </c>
       <c r="H13" s="6" t="n">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="H14" s="6" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="I14" s="9" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         </is>
       </c>
       <c r="H15" s="6" t="n">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         </is>
       </c>
       <c r="H16" s="6" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="I16" s="9" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         </is>
       </c>
       <c r="H17" s="6" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="H18" s="6" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="I18" s="9" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="H19" s="6" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
@@ -1780,12 +1780,12 @@
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>РОЛЬФ</t>
+          <t>ГК АГАТ</t>
         </is>
       </c>
       <c r="E20" s="9" t="inlineStr">
         <is>
-          <t>АО "РОЛЬФ" ONLINE</t>
+          <t>ONLINE ООО "ПЛАТИНУМ" АГАТ</t>
         </is>
       </c>
       <c r="F20" s="9" t="inlineStr">
@@ -1799,7 +1799,7 @@
         </is>
       </c>
       <c r="H20" s="6" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="I20" s="9" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         </is>
       </c>
       <c r="H21" s="6" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c r="H22" s="6" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="I22" s="9" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         </is>
       </c>
       <c r="H23" s="6" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         </is>
       </c>
       <c r="H24" s="6" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="I24" s="9" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         </is>
       </c>
       <c r="H25" s="6" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         </is>
       </c>
       <c r="H26" s="6" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="I26" s="9" t="inlineStr">
         <is>
@@ -2310,7 +2310,7 @@
         </is>
       </c>
       <c r="H27" s="6" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         </is>
       </c>
       <c r="H28" s="6" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="I28" s="9" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Вагнер Авто (СПб)</t>
+          <t>Вагнер Авто / Авторитэйл</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -2456,7 +2456,7 @@
         </is>
       </c>
       <c r="H29" s="6" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
@@ -2529,7 +2529,7 @@
         </is>
       </c>
       <c r="H30" s="6" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="I30" s="9" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         </is>
       </c>
       <c r="H31" s="6" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         </is>
       </c>
       <c r="H32" s="6" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="I32" s="9" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         </is>
       </c>
       <c r="H33" s="6" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         </is>
       </c>
       <c r="H34" s="6" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="I34" s="9" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
         </is>
       </c>
       <c r="H35" s="6" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
@@ -2967,7 +2967,7 @@
         </is>
       </c>
       <c r="H36" s="6" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I36" s="9" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         </is>
       </c>
       <c r="H37" s="6" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
@@ -3113,7 +3113,7 @@
         </is>
       </c>
       <c r="H38" s="6" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="I38" s="9" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         </is>
       </c>
       <c r="H39" s="6" t="n">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         </is>
       </c>
       <c r="H40" s="6" t="n">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="I40" s="9" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="H41" s="6" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
@@ -3405,7 +3405,7 @@
         </is>
       </c>
       <c r="H42" s="6" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="I42" s="9" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         </is>
       </c>
       <c r="H43" s="6" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
@@ -3550,8 +3550,8 @@
           <t>25.07.2026</t>
         </is>
       </c>
-      <c r="H44" s="11" t="n">
-        <v>60</v>
+      <c r="H44" s="6" t="n">
+        <v>66</v>
       </c>
       <c r="I44" s="9" t="inlineStr">
         <is>
@@ -3623,8 +3623,8 @@
           <t>26.07.2026</t>
         </is>
       </c>
-      <c r="H45" s="11" t="n">
-        <v>59</v>
+      <c r="H45" s="6" t="n">
+        <v>65</v>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
@@ -3696,8 +3696,8 @@
           <t>27.07.2026</t>
         </is>
       </c>
-      <c r="H46" s="11" t="n">
-        <v>58</v>
+      <c r="H46" s="6" t="n">
+        <v>64</v>
       </c>
       <c r="I46" s="9" t="inlineStr">
         <is>
@@ -3769,8 +3769,8 @@
           <t>29.07.2026</t>
         </is>
       </c>
-      <c r="H47" s="11" t="n">
-        <v>56</v>
+      <c r="H47" s="6" t="n">
+        <v>62</v>
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
@@ -3842,8 +3842,8 @@
           <t>29.07.2026</t>
         </is>
       </c>
-      <c r="H48" s="11" t="n">
-        <v>56</v>
+      <c r="H48" s="6" t="n">
+        <v>62</v>
       </c>
       <c r="I48" s="9" t="inlineStr">
         <is>
@@ -3915,8 +3915,8 @@
           <t>29.07.2026</t>
         </is>
       </c>
-      <c r="H49" s="11" t="n">
-        <v>56</v>
+      <c r="H49" s="6" t="n">
+        <v>62</v>
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
@@ -3988,8 +3988,8 @@
           <t>29.07.2026</t>
         </is>
       </c>
-      <c r="H50" s="11" t="n">
-        <v>56</v>
+      <c r="H50" s="6" t="n">
+        <v>62</v>
       </c>
       <c r="I50" s="9" t="inlineStr">
         <is>
@@ -4061,8 +4061,8 @@
           <t>30.07.2026</t>
         </is>
       </c>
-      <c r="H51" s="11" t="n">
-        <v>55</v>
+      <c r="H51" s="6" t="n">
+        <v>61</v>
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
@@ -4134,8 +4134,8 @@
           <t>30.07.2026</t>
         </is>
       </c>
-      <c r="H52" s="11" t="n">
-        <v>55</v>
+      <c r="H52" s="6" t="n">
+        <v>61</v>
       </c>
       <c r="I52" s="9" t="inlineStr">
         <is>
@@ -4207,8 +4207,8 @@
           <t>30.07.2026</t>
         </is>
       </c>
-      <c r="H53" s="11" t="n">
-        <v>55</v>
+      <c r="H53" s="6" t="n">
+        <v>61</v>
       </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
@@ -4281,7 +4281,7 @@
         </is>
       </c>
       <c r="H54" s="11" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="I54" s="9" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
         </is>
       </c>
       <c r="H55" s="11" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
@@ -4403,7 +4403,7 @@
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>5030065</t>
+          <t>5389519</t>
         </is>
       </c>
       <c r="D56" s="9" t="inlineStr">
@@ -4427,7 +4427,7 @@
         </is>
       </c>
       <c r="H56" s="11" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="I56" s="9" t="inlineStr">
         <is>
@@ -4500,7 +4500,7 @@
         </is>
       </c>
       <c r="H57" s="11" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         </is>
       </c>
       <c r="H58" s="11" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="I58" s="9" t="inlineStr">
         <is>
@@ -4617,50 +4617,50 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>514610</t>
+          <t>515870</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>5048681</t>
+          <t>5055977</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>РОЛЬФ</t>
+          <t>ГК Форсаж</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>АО "РОЛЬФ" ONLINE</t>
+          <t>ONLINE Форсаж (ООО "ФОРСАЖ")</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>Андрей Кузнецов</t>
+          <t>Светлана Дариенко</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>12.08.2026</t>
+          <t>13.08.2026</t>
         </is>
       </c>
       <c r="H59" s="11" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="I59" s="5" t="inlineStr">
         <is>
-          <t>Belgee</t>
+          <t>JETOUR</t>
         </is>
       </c>
       <c r="J59" s="5" t="inlineStr">
         <is>
-          <t>BELGEE X50+</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="K59" s="5" t="inlineStr">
         <is>
-          <t>Y4K8622ZXTB926121</t>
+          <t>LVTDD24B0TDC38216</t>
         </is>
       </c>
       <c r="L59" s="4" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="O59" s="7" t="inlineStr">
         <is>
-          <t>https://back.sberauto.com/crm/leads/514610</t>
+          <t>https://back.sberauto.com/crm/leads/515870</t>
         </is>
       </c>
     </row>
@@ -4690,50 +4690,50 @@
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>515870</t>
+          <t>523740</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>5055977</t>
+          <t>5085430</t>
         </is>
       </c>
       <c r="D60" s="9" t="inlineStr">
         <is>
-          <t>ГК Форсаж</t>
+          <t>РОЛЬФ</t>
         </is>
       </c>
       <c r="E60" s="9" t="inlineStr">
         <is>
-          <t>ONLINE Форсаж (ООО "ФОРСАЖ")</t>
+          <t>АО "РОЛЬФ" ONLINE</t>
         </is>
       </c>
       <c r="F60" s="9" t="inlineStr">
         <is>
-          <t>Светлана Дариенко</t>
+          <t>Андрей Кузнецов</t>
         </is>
       </c>
       <c r="G60" s="8" t="inlineStr">
         <is>
-          <t>13.08.2026</t>
+          <t>18.08.2026</t>
         </is>
       </c>
       <c r="H60" s="11" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I60" s="9" t="inlineStr">
         <is>
-          <t>JETOUR</t>
+          <t>Belgee</t>
         </is>
       </c>
       <c r="J60" s="9" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>BELGEE X70 FL</t>
         </is>
       </c>
       <c r="K60" s="9" t="inlineStr">
         <is>
-          <t>LVTDD24B0TDC38216</t>
+          <t>Y4K8722D3TB312433</t>
         </is>
       </c>
       <c r="L60" s="8" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="O60" s="10" t="inlineStr">
         <is>
-          <t>https://back.sberauto.com/crm/leads/515870</t>
+          <t>https://back.sberauto.com/crm/leads/523740</t>
         </is>
       </c>
     </row>
@@ -4763,50 +4763,50 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>523750</t>
+          <t>524680</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>5085634</t>
+          <t>5091095</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>РОЛЬФ</t>
+          <t>Автополе</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>АО "РОЛЬФ" ONLINE</t>
+          <t>ООО «Автополе Мото Кудрово» ONLINE</t>
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>Андрей Кузнецов</t>
+          <t>Светлана Дариенко</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>18.08.2026</t>
+          <t>19.08.2026</t>
         </is>
       </c>
       <c r="H61" s="11" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I61" s="5" t="inlineStr">
         <is>
-          <t>Belgee</t>
+          <t>JETOUR</t>
         </is>
       </c>
       <c r="J61" s="5" t="inlineStr">
         <is>
-          <t>BELGEE X70</t>
+          <t>Т2</t>
         </is>
       </c>
       <c r="K61" s="5" t="inlineStr">
         <is>
-          <t>Y4K8722D1TB312768</t>
+          <t>EC3TEUMB3T0003896</t>
         </is>
       </c>
       <c r="L61" s="4" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O61" s="7" t="inlineStr">
         <is>
-          <t>https://back.sberauto.com/crm/leads/523750</t>
+          <t>https://back.sberauto.com/crm/leads/524680</t>
         </is>
       </c>
     </row>
@@ -4836,50 +4836,50 @@
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>523740</t>
+          <t>524616</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>5085430</t>
+          <t>4842498</t>
         </is>
       </c>
       <c r="D62" s="9" t="inlineStr">
         <is>
-          <t>РОЛЬФ</t>
+          <t>ГК Форсаж</t>
         </is>
       </c>
       <c r="E62" s="9" t="inlineStr">
         <is>
-          <t>АО "РОЛЬФ" ONLINE</t>
+          <t>ONLINE Форсаж (ООО "ФОРСАЖ")</t>
         </is>
       </c>
       <c r="F62" s="9" t="inlineStr">
         <is>
-          <t>Андрей Кузнецов</t>
+          <t>Светлана Дариенко</t>
         </is>
       </c>
       <c r="G62" s="8" t="inlineStr">
         <is>
-          <t>18.08.2026</t>
+          <t>19.08.2026</t>
         </is>
       </c>
       <c r="H62" s="11" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I62" s="9" t="inlineStr">
         <is>
-          <t>Belgee</t>
+          <t>JETOUR</t>
         </is>
       </c>
       <c r="J62" s="9" t="inlineStr">
         <is>
-          <t>BELGEE X70 FL</t>
+          <t>Т2</t>
         </is>
       </c>
       <c r="K62" s="9" t="inlineStr">
         <is>
-          <t>Y4K8722D3TB312433</t>
+          <t>EC3TEUMB4T0002580</t>
         </is>
       </c>
       <c r="L62" s="8" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="O62" s="10" t="inlineStr">
         <is>
-          <t>https://back.sberauto.com/crm/leads/523740</t>
+          <t>https://back.sberauto.com/crm/leads/524616</t>
         </is>
       </c>
     </row>
@@ -4909,36 +4909,36 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>524680</t>
+          <t>527058</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>5091095</t>
+          <t>5107053</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>Автополе</t>
+          <t>ГК АГАТ</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>ООО «Автополе Мото Кудрово» ONLINE</t>
+          <t>ONLINE ООО "АРКАДА" АГАТ</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>Светлана Дариенко</t>
+          <t>Андрей Кузнецов</t>
         </is>
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>19.08.2026</t>
+          <t>22.08.2026</t>
         </is>
       </c>
       <c r="H63" s="11" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I63" s="5" t="inlineStr">
         <is>
@@ -4947,12 +4947,12 @@
       </c>
       <c r="J63" s="5" t="inlineStr">
         <is>
-          <t>Т2</t>
+          <t>DASHING</t>
         </is>
       </c>
       <c r="K63" s="5" t="inlineStr">
         <is>
-          <t>EC3TEUMB3T0003896</t>
+          <t>EC3DCUFD4TC015787</t>
         </is>
       </c>
       <c r="L63" s="4" t="inlineStr">
@@ -4972,7 +4972,7 @@
       </c>
       <c r="O63" s="7" t="inlineStr">
         <is>
-          <t>https://back.sberauto.com/crm/leads/524680</t>
+          <t>https://back.sberauto.com/crm/leads/527058</t>
         </is>
       </c>
     </row>
@@ -4982,50 +4982,50 @@
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>524616</t>
+          <t>527028</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>4842498</t>
+          <t>5106805</t>
         </is>
       </c>
       <c r="D64" s="9" t="inlineStr">
         <is>
-          <t>ГК Форсаж</t>
+          <t>РОЛЬФ</t>
         </is>
       </c>
       <c r="E64" s="9" t="inlineStr">
         <is>
-          <t>ONLINE Форсаж (ООО "ФОРСАЖ")</t>
+          <t>АО "РОЛЬФ" ONLINE</t>
         </is>
       </c>
       <c r="F64" s="9" t="inlineStr">
         <is>
-          <t>Светлана Дариенко</t>
+          <t>Андрей Кузнецов</t>
         </is>
       </c>
       <c r="G64" s="8" t="inlineStr">
         <is>
-          <t>19.08.2026</t>
+          <t>22.08.2026</t>
         </is>
       </c>
       <c r="H64" s="11" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I64" s="9" t="inlineStr">
         <is>
-          <t>JETOUR</t>
+          <t>Belgee</t>
         </is>
       </c>
       <c r="J64" s="9" t="inlineStr">
         <is>
-          <t>Т2</t>
+          <t>BELGEE X50+</t>
         </is>
       </c>
       <c r="K64" s="9" t="inlineStr">
         <is>
-          <t>EC3TEUMB4T0002580</t>
+          <t>Y4K8622Z5TB930609</t>
         </is>
       </c>
       <c r="L64" s="8" t="inlineStr">
@@ -5045,7 +5045,7 @@
       </c>
       <c r="O64" s="10" t="inlineStr">
         <is>
-          <t>https://back.sberauto.com/crm/leads/524616</t>
+          <t>https://back.sberauto.com/crm/leads/527028</t>
         </is>
       </c>
     </row>
@@ -5055,22 +5055,22 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>527058</t>
+          <t>526876</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>5107053</t>
+          <t>5106085</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>ГК АГАТ</t>
+          <t>РОЛЬФ</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>ONLINE ООО "АРКАДА" АГАТ</t>
+          <t>АО "РОЛЬФ" ONLINE</t>
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr">
@@ -5084,21 +5084,21 @@
         </is>
       </c>
       <c r="H65" s="11" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="I65" s="5" t="inlineStr">
         <is>
-          <t>JETOUR</t>
+          <t>Belgee</t>
         </is>
       </c>
       <c r="J65" s="5" t="inlineStr">
         <is>
-          <t>DASHING</t>
+          <t>BELGEE X70</t>
         </is>
       </c>
       <c r="K65" s="5" t="inlineStr">
         <is>
-          <t>EC3DCUFD4TC015787</t>
+          <t>Y4K8722D4TB313428</t>
         </is>
       </c>
       <c r="L65" s="4" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="O65" s="7" t="inlineStr">
         <is>
-          <t>https://back.sberauto.com/crm/leads/527058</t>
+          <t>https://back.sberauto.com/crm/leads/526876</t>
         </is>
       </c>
     </row>
@@ -5128,27 +5128,27 @@
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>527028</t>
+          <t>526740</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>5106805</t>
+          <t>5104532</t>
         </is>
       </c>
       <c r="D66" s="9" t="inlineStr">
         <is>
-          <t>РОЛЬФ</t>
+          <t>Сармат</t>
         </is>
       </c>
       <c r="E66" s="9" t="inlineStr">
         <is>
-          <t>АО "РОЛЬФ" ONLINE</t>
+          <t>ООО "САРМАТ" online</t>
         </is>
       </c>
       <c r="F66" s="9" t="inlineStr">
         <is>
-          <t>Андрей Кузнецов</t>
+          <t>Светлана Дариенко</t>
         </is>
       </c>
       <c r="G66" s="8" t="inlineStr">
@@ -5157,31 +5157,31 @@
         </is>
       </c>
       <c r="H66" s="11" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="I66" s="9" t="inlineStr">
         <is>
-          <t>Belgee</t>
+          <t>JETOUR</t>
         </is>
       </c>
       <c r="J66" s="9" t="inlineStr">
         <is>
-          <t>BELGEE X50+</t>
+          <t>X70 PLUS</t>
         </is>
       </c>
       <c r="K66" s="9" t="inlineStr">
         <is>
-          <t>Y4K8622Z5TB930609</t>
+          <t>EC37CUSM1TC006192</t>
         </is>
       </c>
       <c r="L66" s="8" t="inlineStr">
         <is>
-          <t>МП2</t>
+          <t>Online</t>
         </is>
       </c>
       <c r="M66" s="9" t="inlineStr">
         <is>
-          <t>Фокин Борис</t>
+          <t>Фомичев Владислав</t>
         </is>
       </c>
       <c r="N66" s="9" t="inlineStr">
@@ -5191,7 +5191,7 @@
       </c>
       <c r="O66" s="10" t="inlineStr">
         <is>
-          <t>https://back.sberauto.com/crm/leads/527028</t>
+          <t>https://back.sberauto.com/crm/leads/526740</t>
         </is>
       </c>
     </row>
@@ -5201,27 +5201,27 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>526876</t>
+          <t>527104</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>5106085</t>
+          <t>7995</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>РОЛЬФ</t>
+          <t>ФДЦ Авто-Ревю</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>АО "РОЛЬФ" ONLINE</t>
+          <t>ONLINE Авто-Ревю</t>
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>Андрей Кузнецов</t>
+          <t>Валерия Солдатова</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr">
@@ -5230,31 +5230,31 @@
         </is>
       </c>
       <c r="H67" s="11" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="I67" s="5" t="inlineStr">
         <is>
-          <t>Belgee</t>
+          <t>LADA</t>
         </is>
       </c>
       <c r="J67" s="5" t="inlineStr">
         <is>
-          <t>BELGEE X70</t>
+          <t>GRANTA</t>
         </is>
       </c>
       <c r="K67" s="5" t="inlineStr">
         <is>
-          <t>Y4K8722D4TB313428</t>
+          <t>XTA219440T0312015</t>
         </is>
       </c>
       <c r="L67" s="4" t="inlineStr">
         <is>
-          <t>МП2</t>
+          <t>ФДЦ</t>
         </is>
       </c>
       <c r="M67" s="5" t="inlineStr">
         <is>
-          <t>Фокин Борис</t>
+          <t>Яковлева Валерия</t>
         </is>
       </c>
       <c r="N67" s="5" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="O67" s="7" t="inlineStr">
         <is>
-          <t>https://back.sberauto.com/crm/leads/526876</t>
+          <t>https://back.sberauto.com/crm/leads/527104</t>
         </is>
       </c>
     </row>
@@ -5274,27 +5274,27 @@
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>526740</t>
+          <t>526542</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>5104532</t>
+          <t>5104166</t>
         </is>
       </c>
       <c r="D68" s="9" t="inlineStr">
         <is>
-          <t>Сармат</t>
+          <t>Чери Автофорум</t>
         </is>
       </c>
       <c r="E68" s="9" t="inlineStr">
         <is>
-          <t>ООО "САРМАТ" online</t>
+          <t>ООО "АВТОФОРУМ" ONLINE</t>
         </is>
       </c>
       <c r="F68" s="9" t="inlineStr">
         <is>
-          <t>Светлана Дариенко</t>
+          <t>Андрей Кузнецов</t>
         </is>
       </c>
       <c r="G68" s="8" t="inlineStr">
@@ -5303,7 +5303,7 @@
         </is>
       </c>
       <c r="H68" s="11" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="I68" s="9" t="inlineStr">
         <is>
@@ -5312,22 +5312,22 @@
       </c>
       <c r="J68" s="9" t="inlineStr">
         <is>
-          <t>X70 PLUS</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="K68" s="9" t="inlineStr">
         <is>
-          <t>EC37CUSM1TC006192</t>
+          <t>LVTDD24B8TDB98922</t>
         </is>
       </c>
       <c r="L68" s="8" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>МП2</t>
         </is>
       </c>
       <c r="M68" s="9" t="inlineStr">
         <is>
-          <t>Фомичев Владислав</t>
+          <t>Фокин Борис</t>
         </is>
       </c>
       <c r="N68" s="9" t="inlineStr">
@@ -5337,7 +5337,7 @@
       </c>
       <c r="O68" s="10" t="inlineStr">
         <is>
-          <t>https://back.sberauto.com/crm/leads/526740</t>
+          <t>https://back.sberauto.com/crm/leads/526542</t>
         </is>
       </c>
     </row>
@@ -5347,60 +5347,60 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>527104</t>
+          <t>527422</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>7995</t>
+          <t>4045445</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>ФДЦ Авто-Ревю</t>
+          <t>Автохолдинг Максимум</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
         <is>
-          <t>ONLINE Авто-Ревю</t>
+          <t>ООО "МАКСИМУМ КРЕДИТ" online</t>
         </is>
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>Валерия Солдатова</t>
+          <t>Светлана Дариенко</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>22.08.2026</t>
+          <t>23.08.2026</t>
         </is>
       </c>
       <c r="H69" s="11" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I69" s="5" t="inlineStr">
         <is>
-          <t>LADA</t>
+          <t>JETOUR</t>
         </is>
       </c>
       <c r="J69" s="5" t="inlineStr">
         <is>
-          <t>GRANTA</t>
+          <t>X70+</t>
         </is>
       </c>
       <c r="K69" s="5" t="inlineStr">
         <is>
-          <t>XTA219440T0312015</t>
+          <t>527422</t>
         </is>
       </c>
       <c r="L69" s="4" t="inlineStr">
         <is>
-          <t>ФДЦ</t>
+          <t>МП2</t>
         </is>
       </c>
       <c r="M69" s="5" t="inlineStr">
         <is>
-          <t>Яковлева Валерия</t>
+          <t>Фокин Борис</t>
         </is>
       </c>
       <c r="N69" s="5" t="inlineStr">
@@ -5410,7 +5410,7 @@
       </c>
       <c r="O69" s="7" t="inlineStr">
         <is>
-          <t>https://back.sberauto.com/crm/leads/527104</t>
+          <t>https://back.sberauto.com/crm/leads/527422</t>
         </is>
       </c>
     </row>
@@ -5420,22 +5420,22 @@
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>526542</t>
+          <t>527604</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>5104166</t>
+          <t>5111482</t>
         </is>
       </c>
       <c r="D70" s="9" t="inlineStr">
         <is>
-          <t>Чери Автофорум</t>
+          <t>РОЛЬФ</t>
         </is>
       </c>
       <c r="E70" s="9" t="inlineStr">
         <is>
-          <t>ООО "АВТОФОРУМ" ONLINE</t>
+          <t>АО "РОЛЬФ" ONLINE</t>
         </is>
       </c>
       <c r="F70" s="9" t="inlineStr">
@@ -5445,25 +5445,25 @@
       </c>
       <c r="G70" s="8" t="inlineStr">
         <is>
-          <t>22.08.2026</t>
+          <t>23.08.2026</t>
         </is>
       </c>
       <c r="H70" s="11" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I70" s="9" t="inlineStr">
         <is>
-          <t>JETOUR</t>
+          <t>Geely</t>
         </is>
       </c>
       <c r="J70" s="9" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>GEELY CITYRAY</t>
         </is>
       </c>
       <c r="K70" s="9" t="inlineStr">
         <is>
-          <t>LVTDD24B8TDB98922</t>
+          <t>LB3G43S94TX409300</t>
         </is>
       </c>
       <c r="L70" s="8" t="inlineStr">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="O70" s="10" t="inlineStr">
         <is>
-          <t>https://back.sberauto.com/crm/leads/526542</t>
+          <t>https://back.sberauto.com/crm/leads/527604</t>
         </is>
       </c>
     </row>
@@ -5493,27 +5493,27 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>527422</t>
+          <t>527526</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>4045445</t>
+          <t>5110893</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>Автохолдинг Максимум</t>
+          <t>РОЛЬФ</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>ООО "МАКСИМУМ КРЕДИТ" online</t>
+          <t>АО "РОЛЬФ" ONLINE</t>
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>Светлана Дариенко</t>
+          <t>Андрей Кузнецов</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr">
@@ -5522,21 +5522,21 @@
         </is>
       </c>
       <c r="H71" s="11" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="I71" s="5" t="inlineStr">
         <is>
-          <t>JETOUR</t>
+          <t>Belgee</t>
         </is>
       </c>
       <c r="J71" s="5" t="inlineStr">
         <is>
-          <t>X70+</t>
+          <t>BELGEE Х50+</t>
         </is>
       </c>
       <c r="K71" s="5" t="inlineStr">
         <is>
-          <t>527422</t>
+          <t>Y4K8622ZXTB929102</t>
         </is>
       </c>
       <c r="L71" s="4" t="inlineStr">
@@ -5556,7 +5556,7 @@
       </c>
       <c r="O71" s="7" t="inlineStr">
         <is>
-          <t>https://back.sberauto.com/crm/leads/527422</t>
+          <t>https://back.sberauto.com/crm/leads/527526</t>
         </is>
       </c>
     </row>
@@ -5566,12 +5566,12 @@
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>527604</t>
+          <t>529470</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>5111482</t>
+          <t>5124407</t>
         </is>
       </c>
       <c r="D72" s="9" t="inlineStr">
@@ -5591,11 +5591,11 @@
       </c>
       <c r="G72" s="8" t="inlineStr">
         <is>
-          <t>23.08.2026</t>
+          <t>25.08.2026</t>
         </is>
       </c>
       <c r="H72" s="11" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I72" s="9" t="inlineStr">
         <is>
@@ -5604,12 +5604,12 @@
       </c>
       <c r="J72" s="9" t="inlineStr">
         <is>
-          <t>GEELY CITYRAY</t>
+          <t>GEELY MONJARO</t>
         </is>
       </c>
       <c r="K72" s="9" t="inlineStr">
         <is>
-          <t>LB3G43S94TX409300</t>
+          <t>LB37852D3TS046120</t>
         </is>
       </c>
       <c r="L72" s="8" t="inlineStr">
@@ -5629,7 +5629,7 @@
       </c>
       <c r="O72" s="10" t="inlineStr">
         <is>
-          <t>https://back.sberauto.com/crm/leads/527604</t>
+          <t>https://back.sberauto.com/crm/leads/529470</t>
         </is>
       </c>
     </row>
@@ -5639,60 +5639,60 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>527526</t>
+          <t>530302</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>5110893</t>
+          <t>4837879</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>РОЛЬФ</t>
+          <t>Приоритет_ГК КАН Авто</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
         <is>
-          <t>АО "РОЛЬФ" ONLINE</t>
+          <t>ONLINE Кан Авто-11</t>
         </is>
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>Андрей Кузнецов</t>
+          <t>Алексей Чихарев</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
-          <t>23.08.2026</t>
+          <t>26.08.2026</t>
         </is>
       </c>
       <c r="H73" s="11" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I73" s="5" t="inlineStr">
         <is>
-          <t>Belgee</t>
+          <t>LADA</t>
         </is>
       </c>
       <c r="J73" s="5" t="inlineStr">
         <is>
-          <t>BELGEE Х50+</t>
+          <t>GRANTA</t>
         </is>
       </c>
       <c r="K73" s="5" t="inlineStr">
         <is>
-          <t>Y4K8622ZXTB929102</t>
+          <t>530302</t>
         </is>
       </c>
       <c r="L73" s="4" t="inlineStr">
         <is>
-          <t>МП2</t>
+          <t>ФДЦ+ГП</t>
         </is>
       </c>
       <c r="M73" s="5" t="inlineStr">
         <is>
-          <t>Фокин Борис</t>
+          <t>Горбунов Роман</t>
         </is>
       </c>
       <c r="N73" s="5" t="inlineStr">
@@ -5702,7 +5702,7 @@
       </c>
       <c r="O73" s="7" t="inlineStr">
         <is>
-          <t>https://back.sberauto.com/crm/leads/527526</t>
+          <t>https://back.sberauto.com/crm/leads/530302</t>
         </is>
       </c>
     </row>
@@ -5712,60 +5712,60 @@
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>529470</t>
+          <t>530360</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>5124407</t>
+          <t>5007440</t>
         </is>
       </c>
       <c r="D74" s="9" t="inlineStr">
         <is>
-          <t>РОЛЬФ</t>
+          <t>Ринг Авто</t>
         </is>
       </c>
       <c r="E74" s="9" t="inlineStr">
         <is>
-          <t>АО "РОЛЬФ" ONLINE</t>
+          <t>ONLINE ООО "РИНГ СЕРВИС" ВОРОНЕЖ</t>
         </is>
       </c>
       <c r="F74" s="9" t="inlineStr">
         <is>
-          <t>Андрей Кузнецов</t>
+          <t>Валерия Солдатова</t>
         </is>
       </c>
       <c r="G74" s="8" t="inlineStr">
         <is>
-          <t>25.08.2026</t>
-        </is>
-      </c>
-      <c r="H74" s="12" t="n">
-        <v>29</v>
+          <t>26.08.2026</t>
+        </is>
+      </c>
+      <c r="H74" s="11" t="n">
+        <v>34</v>
       </c>
       <c r="I74" s="9" t="inlineStr">
         <is>
-          <t>Geely</t>
+          <t>JETOUR</t>
         </is>
       </c>
       <c r="J74" s="9" t="inlineStr">
         <is>
-          <t>GEELY MONJARO</t>
+          <t>DASHING</t>
         </is>
       </c>
       <c r="K74" s="9" t="inlineStr">
         <is>
-          <t>LB37852D3TS046120</t>
+          <t>EC3DLUFD3TC013903</t>
         </is>
       </c>
       <c r="L74" s="8" t="inlineStr">
         <is>
-          <t>МП2</t>
+          <t>ФДЦ</t>
         </is>
       </c>
       <c r="M74" s="9" t="inlineStr">
         <is>
-          <t>Фокин Борис</t>
+          <t>Григорян Михаил</t>
         </is>
       </c>
       <c r="N74" s="9" t="inlineStr">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="O74" s="10" t="inlineStr">
         <is>
-          <t>https://back.sberauto.com/crm/leads/529470</t>
+          <t>https://back.sberauto.com/crm/leads/530360</t>
         </is>
       </c>
     </row>
@@ -5785,50 +5785,50 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>529444</t>
+          <t>531994</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>5122811</t>
+          <t>3250566</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>ХОТЭЙ АВТО Ярославль</t>
+          <t>ГК КОРС Джетур</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>ХОТЭЙ АВТО online</t>
+          <t>ООО "КОРС НОВОМОСКОВСК" ONLINE</t>
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>Алексей Чихарев</t>
+          <t>Андрей Кузнецов</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr">
         <is>
-          <t>25.08.2026</t>
-        </is>
-      </c>
-      <c r="H75" s="12" t="n">
-        <v>29</v>
+          <t>28.08.2026</t>
+        </is>
+      </c>
+      <c r="H75" s="11" t="n">
+        <v>32</v>
       </c>
       <c r="I75" s="5" t="inlineStr">
         <is>
-          <t>SOUEAST</t>
+          <t>JETOUR</t>
         </is>
       </c>
       <c r="J75" s="5" t="inlineStr">
         <is>
-          <t>S 07</t>
+          <t>Х70+</t>
         </is>
       </c>
       <c r="K75" s="5" t="inlineStr">
         <is>
-          <t>EC37PUSA2TC200711</t>
+          <t>531994</t>
         </is>
       </c>
       <c r="L75" s="4" t="inlineStr">
@@ -5848,7 +5848,7 @@
       </c>
       <c r="O75" s="7" t="inlineStr">
         <is>
-          <t>https://back.sberauto.com/crm/leads/529444</t>
+          <t>https://back.sberauto.com/crm/leads/531994</t>
         </is>
       </c>
     </row>
@@ -5858,60 +5858,60 @@
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>530302</t>
+          <t>532144</t>
         </is>
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t>4837879</t>
+          <t>5144634</t>
         </is>
       </c>
       <c r="D76" s="9" t="inlineStr">
         <is>
-          <t>Приоритет_ГК КАН Авто</t>
+          <t>РОЛЬФ</t>
         </is>
       </c>
       <c r="E76" s="9" t="inlineStr">
         <is>
-          <t>ONLINE Кан Авто-11</t>
+          <t>АО "РОЛЬФ" ONLINE</t>
         </is>
       </c>
       <c r="F76" s="9" t="inlineStr">
         <is>
-          <t>Алексей Чихарев</t>
+          <t>Андрей Кузнецов</t>
         </is>
       </c>
       <c r="G76" s="8" t="inlineStr">
         <is>
-          <t>26.08.2026</t>
-        </is>
-      </c>
-      <c r="H76" s="12" t="n">
-        <v>28</v>
+          <t>28.08.2026</t>
+        </is>
+      </c>
+      <c r="H76" s="11" t="n">
+        <v>32</v>
       </c>
       <c r="I76" s="9" t="inlineStr">
         <is>
-          <t>LADA</t>
+          <t>Geely</t>
         </is>
       </c>
       <c r="J76" s="9" t="inlineStr">
         <is>
-          <t>GRANTA</t>
+          <t>GEELY PREFACE</t>
         </is>
       </c>
       <c r="K76" s="9" t="inlineStr">
         <is>
-          <t>530302</t>
+          <t>L6TFS1S80TD006828</t>
         </is>
       </c>
       <c r="L76" s="8" t="inlineStr">
         <is>
-          <t>ФДЦ+ГП</t>
+          <t>МП2</t>
         </is>
       </c>
       <c r="M76" s="9" t="inlineStr">
         <is>
-          <t>Горбунов Роман</t>
+          <t>Фокин Борис</t>
         </is>
       </c>
       <c r="N76" s="9" t="inlineStr">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="O76" s="10" t="inlineStr">
         <is>
-          <t>https://back.sberauto.com/crm/leads/530302</t>
+          <t>https://back.sberauto.com/crm/leads/532144</t>
         </is>
       </c>
     </row>
@@ -5931,36 +5931,36 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>530360</t>
+          <t>531978</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>5007440</t>
+          <t>5018424</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>Ринг Авто</t>
+          <t>Элке Авто</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
         <is>
-          <t>ONLINE ООО "РИНГ СЕРВИС" ВОРОНЕЖ</t>
+          <t>ООО "ЭЛКЕ АВТО" ONLINE</t>
         </is>
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>Валерия Солдатова</t>
+          <t>Светлана Дариенко</t>
         </is>
       </c>
       <c r="G77" s="4" t="inlineStr">
         <is>
-          <t>26.08.2026</t>
-        </is>
-      </c>
-      <c r="H77" s="12" t="n">
-        <v>28</v>
+          <t>28.08.2026</t>
+        </is>
+      </c>
+      <c r="H77" s="11" t="n">
+        <v>32</v>
       </c>
       <c r="I77" s="5" t="inlineStr">
         <is>
@@ -5969,22 +5969,22 @@
       </c>
       <c r="J77" s="5" t="inlineStr">
         <is>
-          <t>DASHING</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="K77" s="5" t="inlineStr">
         <is>
-          <t>EC3DLUFD3TC013903</t>
+          <t>EC3TEUMB7T0003948</t>
         </is>
       </c>
       <c r="L77" s="4" t="inlineStr">
         <is>
-          <t>ФДЦ</t>
+          <t>МП2</t>
         </is>
       </c>
       <c r="M77" s="5" t="inlineStr">
         <is>
-          <t>Григорян Михаил</t>
+          <t>Фокин Борис</t>
         </is>
       </c>
       <c r="N77" s="5" t="inlineStr">
@@ -5994,7 +5994,7 @@
       </c>
       <c r="O77" s="7" t="inlineStr">
         <is>
-          <t>https://back.sberauto.com/crm/leads/530360</t>
+          <t>https://back.sberauto.com/crm/leads/531978</t>
         </is>
       </c>
     </row>
@@ -6004,36 +6004,36 @@
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>531994</t>
+          <t>533134</t>
         </is>
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
-          <t>3250566</t>
+          <t>5151131</t>
         </is>
       </c>
       <c r="D78" s="9" t="inlineStr">
         <is>
-          <t>ГК КОРС Джетур</t>
+          <t>АлексМоторс</t>
         </is>
       </c>
       <c r="E78" s="9" t="inlineStr">
         <is>
-          <t>ООО "КОРС НОВОМОСКОВСК" ONLINE</t>
+          <t>АЛЕКСМОТОРС ONLINE</t>
         </is>
       </c>
       <c r="F78" s="9" t="inlineStr">
         <is>
-          <t>Андрей Кузнецов</t>
+          <t>Светлана Дариенко</t>
         </is>
       </c>
       <c r="G78" s="8" t="inlineStr">
         <is>
-          <t>28.08.2026</t>
-        </is>
-      </c>
-      <c r="H78" s="12" t="n">
-        <v>26</v>
+          <t>29.08.2026</t>
+        </is>
+      </c>
+      <c r="H78" s="11" t="n">
+        <v>31</v>
       </c>
       <c r="I78" s="9" t="inlineStr">
         <is>
@@ -6042,12 +6042,12 @@
       </c>
       <c r="J78" s="9" t="inlineStr">
         <is>
-          <t>Х70+</t>
+          <t>DASHING</t>
         </is>
       </c>
       <c r="K78" s="9" t="inlineStr">
         <is>
-          <t>531994</t>
+          <t>EC3DCUFD6TC016178</t>
         </is>
       </c>
       <c r="L78" s="8" t="inlineStr">
@@ -6067,7 +6067,7 @@
       </c>
       <c r="O78" s="10" t="inlineStr">
         <is>
-          <t>https://back.sberauto.com/crm/leads/531994</t>
+          <t>https://back.sberauto.com/crm/leads/533134</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>532144</t>
+          <t>533290</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>5144634</t>
+          <t>5152148</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
@@ -6102,25 +6102,25 @@
       </c>
       <c r="G79" s="4" t="inlineStr">
         <is>
-          <t>28.08.2026</t>
-        </is>
-      </c>
-      <c r="H79" s="12" t="n">
-        <v>26</v>
+          <t>29.08.2026</t>
+        </is>
+      </c>
+      <c r="H79" s="11" t="n">
+        <v>31</v>
       </c>
       <c r="I79" s="5" t="inlineStr">
         <is>
-          <t>Geely</t>
+          <t>Belgee</t>
         </is>
       </c>
       <c r="J79" s="5" t="inlineStr">
         <is>
-          <t>GEELY PREFACE</t>
+          <t>BELGEE S50 AT</t>
         </is>
       </c>
       <c r="K79" s="5" t="inlineStr">
         <is>
-          <t>L6TFS1S80TD006828</t>
+          <t>Y4K8824Z5TB206457</t>
         </is>
       </c>
       <c r="L79" s="4" t="inlineStr">
@@ -6140,7 +6140,7 @@
       </c>
       <c r="O79" s="7" t="inlineStr">
         <is>
-          <t>https://back.sberauto.com/crm/leads/532144</t>
+          <t>https://back.sberauto.com/crm/leads/533290</t>
         </is>
       </c>
     </row>
@@ -6150,36 +6150,36 @@
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>531978</t>
+          <t>533890</t>
         </is>
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t>5018424</t>
+          <t>5149333</t>
         </is>
       </c>
       <c r="D80" s="9" t="inlineStr">
         <is>
-          <t>Элке Авто</t>
+          <t>Радар-Авто</t>
         </is>
       </c>
       <c r="E80" s="9" t="inlineStr">
         <is>
-          <t>ООО "ЭЛКЕ АВТО" ONLINE</t>
+          <t>ООО "ЛАДА ИВАНОВО" / Радар-Авто online</t>
         </is>
       </c>
       <c r="F80" s="9" t="inlineStr">
         <is>
-          <t>Светлана Дариенко</t>
+          <t>Алексей Чихарев</t>
         </is>
       </c>
       <c r="G80" s="8" t="inlineStr">
         <is>
-          <t>28.08.2026</t>
-        </is>
-      </c>
-      <c r="H80" s="12" t="n">
-        <v>26</v>
+          <t>29.08.2026</t>
+        </is>
+      </c>
+      <c r="H80" s="11" t="n">
+        <v>31</v>
       </c>
       <c r="I80" s="9" t="inlineStr">
         <is>
@@ -6188,12 +6188,12 @@
       </c>
       <c r="J80" s="9" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>DASHING</t>
         </is>
       </c>
       <c r="K80" s="9" t="inlineStr">
         <is>
-          <t>EC3TEUMB7T0003948</t>
+          <t>EC3DCUFD9TC015980</t>
         </is>
       </c>
       <c r="L80" s="8" t="inlineStr">
@@ -6213,7 +6213,7 @@
       </c>
       <c r="O80" s="10" t="inlineStr">
         <is>
-          <t>https://back.sberauto.com/crm/leads/531978</t>
+          <t>https://back.sberauto.com/crm/leads/533890</t>
         </is>
       </c>
     </row>
@@ -6223,27 +6223,27 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>533134</t>
+          <t>533850</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>5151131</t>
+          <t>5150148</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>АлексМоторс</t>
+          <t>Чери Автофорум</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
         <is>
-          <t>АЛЕКСМОТОРС ONLINE</t>
+          <t>ONLINE CHERY Автофорум (ООО "АВТОФОРУМ ЦЕНТР")</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>Светлана Дариенко</t>
+          <t>Евгения Добролюбова</t>
         </is>
       </c>
       <c r="G81" s="4" t="inlineStr">
@@ -6251,22 +6251,22 @@
           <t>29.08.2026</t>
         </is>
       </c>
-      <c r="H81" s="12" t="n">
-        <v>25</v>
+      <c r="H81" s="11" t="n">
+        <v>31</v>
       </c>
       <c r="I81" s="5" t="inlineStr">
         <is>
-          <t>JETOUR</t>
+          <t>SOUEAST</t>
         </is>
       </c>
       <c r="J81" s="5" t="inlineStr">
         <is>
-          <t>DASHING</t>
+          <t>S06</t>
         </is>
       </c>
       <c r="K81" s="5" t="inlineStr">
         <is>
-          <t>EC3DCUFD6TC016178</t>
+          <t>EC3DCUFD0TC000414</t>
         </is>
       </c>
       <c r="L81" s="4" t="inlineStr">
@@ -6286,7 +6286,7 @@
       </c>
       <c r="O81" s="7" t="inlineStr">
         <is>
-          <t>https://back.sberauto.com/crm/leads/533134</t>
+          <t>https://back.sberauto.com/crm/leads/533850</t>
         </is>
       </c>
     </row>
@@ -6296,50 +6296,50 @@
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>533290</t>
+          <t>534400</t>
         </is>
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t>5152148</t>
+          <t>5158568</t>
         </is>
       </c>
       <c r="D82" s="9" t="inlineStr">
         <is>
-          <t>РОЛЬФ</t>
+          <t>Вагнер Авто / Авторитэйл</t>
         </is>
       </c>
       <c r="E82" s="9" t="inlineStr">
         <is>
-          <t>АО "РОЛЬФ" ONLINE</t>
+          <t>ONLINE ООО "АВТОРИТЭЙЛ М" СПБ</t>
         </is>
       </c>
       <c r="F82" s="9" t="inlineStr">
         <is>
-          <t>Андрей Кузнецов</t>
+          <t>Светлана Дариенко</t>
         </is>
       </c>
       <c r="G82" s="8" t="inlineStr">
         <is>
-          <t>29.08.2026</t>
+          <t>30.08.2026</t>
         </is>
       </c>
       <c r="H82" s="12" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I82" s="9" t="inlineStr">
         <is>
-          <t>Belgee</t>
+          <t>JETOUR</t>
         </is>
       </c>
       <c r="J82" s="9" t="inlineStr">
         <is>
-          <t>BELGEE S50 AT</t>
+          <t>X70 PLUS</t>
         </is>
       </c>
       <c r="K82" s="9" t="inlineStr">
         <is>
-          <t>Y4K8824Z5TB206457</t>
+          <t>EC37CUSM2TC005990</t>
         </is>
       </c>
       <c r="L82" s="8" t="inlineStr">
@@ -6359,7 +6359,7 @@
       </c>
       <c r="O82" s="10" t="inlineStr">
         <is>
-          <t>https://back.sberauto.com/crm/leads/533290</t>
+          <t>https://back.sberauto.com/crm/leads/534400</t>
         </is>
       </c>
     </row>
@@ -6369,36 +6369,36 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>533890</t>
+          <t>534164</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>5149333</t>
+          <t>5157539</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>Радар-Авто</t>
+          <t>ГК АГАТ</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
         <is>
-          <t>ООО "ЛАДА ИВАНОВО" / Радар-Авто online</t>
+          <t>ООО "МАКСИМА АВТО" online</t>
         </is>
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>Алексей Чихарев</t>
+          <t>Андрей Кузнецов</t>
         </is>
       </c>
       <c r="G83" s="4" t="inlineStr">
         <is>
-          <t>29.08.2026</t>
+          <t>30.08.2026</t>
         </is>
       </c>
       <c r="H83" s="12" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I83" s="5" t="inlineStr">
         <is>
@@ -6407,12 +6407,12 @@
       </c>
       <c r="J83" s="5" t="inlineStr">
         <is>
-          <t>DASHING</t>
+          <t>X 70 PLUS</t>
         </is>
       </c>
       <c r="K83" s="5" t="inlineStr">
         <is>
-          <t>EC3DCUFD9TC015980</t>
+          <t>EC37CUSM4TC006915</t>
         </is>
       </c>
       <c r="L83" s="4" t="inlineStr">
@@ -6432,7 +6432,7 @@
       </c>
       <c r="O83" s="7" t="inlineStr">
         <is>
-          <t>https://back.sberauto.com/crm/leads/533890</t>
+          <t>https://back.sberauto.com/crm/leads/534164</t>
         </is>
       </c>
     </row>
@@ -6442,50 +6442,50 @@
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>533850</t>
+          <t>534070</t>
         </is>
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t>5150148</t>
+          <t>5156570</t>
         </is>
       </c>
       <c r="D84" s="9" t="inlineStr">
         <is>
-          <t>Чери Автофорум</t>
+          <t>Приоритет_ГК КАН Авто</t>
         </is>
       </c>
       <c r="E84" s="9" t="inlineStr">
         <is>
-          <t>ONLINE CHERY Автофорум (ООО "АВТОФОРУМ ЦЕНТР")</t>
+          <t>ООО "КАН АВТО-5" ONLINE</t>
         </is>
       </c>
       <c r="F84" s="9" t="inlineStr">
         <is>
-          <t>Евгения Добролюбова</t>
+          <t>Алексей Чихарев</t>
         </is>
       </c>
       <c r="G84" s="8" t="inlineStr">
         <is>
-          <t>29.08.2026</t>
+          <t>30.08.2026</t>
         </is>
       </c>
       <c r="H84" s="12" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I84" s="9" t="inlineStr">
         <is>
-          <t>SOUEAST</t>
+          <t>JETOUR</t>
         </is>
       </c>
       <c r="J84" s="9" t="inlineStr">
         <is>
-          <t>S06</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="K84" s="9" t="inlineStr">
         <is>
-          <t>EC3DCUFD0TC000414</t>
+          <t>LVTDD24B3TDB74138</t>
         </is>
       </c>
       <c r="L84" s="8" t="inlineStr">
@@ -6505,7 +6505,7 @@
       </c>
       <c r="O84" s="10" t="inlineStr">
         <is>
-          <t>https://back.sberauto.com/crm/leads/533850</t>
+          <t>https://back.sberauto.com/crm/leads/534070</t>
         </is>
       </c>
     </row>
@@ -6515,22 +6515,22 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>534164</t>
+          <t>534261</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>5157539</t>
+          <t>3231162</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>ГК АГАТ</t>
+          <t>РОЛЬФ</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
         <is>
-          <t>ООО "МАКСИМА АВТО" online</t>
+          <t>АО "РОЛЬФ" ONLINE</t>
         </is>
       </c>
       <c r="F85" s="5" t="inlineStr">
@@ -6544,21 +6544,21 @@
         </is>
       </c>
       <c r="H85" s="12" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I85" s="5" t="inlineStr">
         <is>
-          <t>JETOUR</t>
+          <t>Belgee</t>
         </is>
       </c>
       <c r="J85" s="5" t="inlineStr">
         <is>
-          <t>X 70 PLUS</t>
+          <t>BELGEE X50+</t>
         </is>
       </c>
       <c r="K85" s="5" t="inlineStr">
         <is>
-          <t>EC37CUSM4TC006915</t>
+          <t>Y4K8622Z5TB934305</t>
         </is>
       </c>
       <c r="L85" s="4" t="inlineStr">
@@ -6578,7 +6578,7 @@
       </c>
       <c r="O85" s="7" t="inlineStr">
         <is>
-          <t>https://back.sberauto.com/crm/leads/534164</t>
+          <t>https://back.sberauto.com/crm/leads/534261</t>
         </is>
       </c>
     </row>
@@ -6588,27 +6588,27 @@
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>534400</t>
+          <t>533980</t>
         </is>
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t>5158568</t>
+          <t>5156058</t>
         </is>
       </c>
       <c r="D86" s="9" t="inlineStr">
         <is>
-          <t>ГК Авторитэйл М</t>
+          <t>РОЛЬФ</t>
         </is>
       </c>
       <c r="E86" s="9" t="inlineStr">
         <is>
-          <t>ONLINE ООО "АВТОРИТЭЙЛ М" СПБ</t>
+          <t>АО "РОЛЬФ" ONLINE</t>
         </is>
       </c>
       <c r="F86" s="9" t="inlineStr">
         <is>
-          <t>Светлана Дариенко</t>
+          <t>Андрей Кузнецов</t>
         </is>
       </c>
       <c r="G86" s="8" t="inlineStr">
@@ -6617,21 +6617,21 @@
         </is>
       </c>
       <c r="H86" s="12" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I86" s="9" t="inlineStr">
         <is>
-          <t>JETOUR</t>
+          <t>Geely</t>
         </is>
       </c>
       <c r="J86" s="9" t="inlineStr">
         <is>
-          <t>X70 PLUS</t>
+          <t>GEELY EX5 EM-R</t>
         </is>
       </c>
       <c r="K86" s="9" t="inlineStr">
         <is>
-          <t>EC37CUSM2TC005990</t>
+          <t>LB3P11SN7TH391475</t>
         </is>
       </c>
       <c r="L86" s="8" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="O86" s="10" t="inlineStr">
         <is>
-          <t>https://back.sberauto.com/crm/leads/534400</t>
+          <t>https://back.sberauto.com/crm/leads/533980</t>
         </is>
       </c>
     </row>
@@ -6661,36 +6661,36 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>534070</t>
+          <t>534986</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>5156570</t>
+          <t>5163119</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>Приоритет_ГК КАН Авто</t>
+          <t>Fresh Auto</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
         <is>
-          <t>ООО "КАН АВТО-5" ONLINE</t>
+          <t>ONLINE ООО "ФРЕШ-К"</t>
         </is>
       </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
-          <t>Алексей Чихарев</t>
+          <t>Андрей Кузнецов</t>
         </is>
       </c>
       <c r="G87" s="4" t="inlineStr">
         <is>
-          <t>30.08.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="H87" s="12" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I87" s="5" t="inlineStr">
         <is>
@@ -6699,12 +6699,12 @@
       </c>
       <c r="J87" s="5" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>DASHING</t>
         </is>
       </c>
       <c r="K87" s="5" t="inlineStr">
         <is>
-          <t>LVTDD24B3TDB74138</t>
+          <t>EC3DLUFD2TC012452</t>
         </is>
       </c>
       <c r="L87" s="4" t="inlineStr">
@@ -6724,7 +6724,7 @@
       </c>
       <c r="O87" s="7" t="inlineStr">
         <is>
-          <t>https://back.sberauto.com/crm/leads/534070</t>
+          <t>https://back.sberauto.com/crm/leads/534986</t>
         </is>
       </c>
     </row>
@@ -6734,12 +6734,12 @@
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>534261</t>
+          <t>535468</t>
         </is>
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t>3231162</t>
+          <t>5116289</t>
         </is>
       </c>
       <c r="D88" s="9" t="inlineStr">
@@ -6759,25 +6759,25 @@
       </c>
       <c r="G88" s="8" t="inlineStr">
         <is>
-          <t>30.08.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="H88" s="12" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I88" s="9" t="inlineStr">
         <is>
-          <t>Belgee</t>
+          <t>Geely</t>
         </is>
       </c>
       <c r="J88" s="9" t="inlineStr">
         <is>
-          <t>BELGEE X50+</t>
+          <t>GEELY CITYRAY</t>
         </is>
       </c>
       <c r="K88" s="9" t="inlineStr">
         <is>
-          <t>Y4K8622Z5TB934305</t>
+          <t>LB3G43S96TX415101</t>
         </is>
       </c>
       <c r="L88" s="8" t="inlineStr">
@@ -6797,7 +6797,7 @@
       </c>
       <c r="O88" s="10" t="inlineStr">
         <is>
-          <t>https://back.sberauto.com/crm/leads/534261</t>
+          <t>https://back.sberauto.com/crm/leads/535468</t>
         </is>
       </c>
     </row>
@@ -6807,12 +6807,12 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>533980</t>
+          <t>535440</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>5156058</t>
+          <t>5166372</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
@@ -6832,25 +6832,25 @@
       </c>
       <c r="G89" s="4" t="inlineStr">
         <is>
-          <t>30.08.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="H89" s="12" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I89" s="5" t="inlineStr">
         <is>
-          <t>Geely</t>
+          <t>JELAND</t>
         </is>
       </c>
       <c r="J89" s="5" t="inlineStr">
         <is>
-          <t>GEELY EX5 EM-R</t>
+          <t>J6 AWD</t>
         </is>
       </c>
       <c r="K89" s="5" t="inlineStr">
         <is>
-          <t>LB3P11SN7TH391475</t>
+          <t>EDXDD21B2TG031200</t>
         </is>
       </c>
       <c r="L89" s="4" t="inlineStr">
@@ -6870,7 +6870,7 @@
       </c>
       <c r="O89" s="7" t="inlineStr">
         <is>
-          <t>https://back.sberauto.com/crm/leads/533980</t>
+          <t>https://back.sberauto.com/crm/leads/535440</t>
         </is>
       </c>
     </row>
@@ -6880,22 +6880,22 @@
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>534986</t>
+          <t>534742</t>
         </is>
       </c>
       <c r="C90" s="8" t="inlineStr">
         <is>
-          <t>5163119</t>
+          <t>1232677</t>
         </is>
       </c>
       <c r="D90" s="9" t="inlineStr">
         <is>
-          <t>Fresh Auto</t>
+          <t>РОЛЬФ</t>
         </is>
       </c>
       <c r="E90" s="9" t="inlineStr">
         <is>
-          <t>ONLINE ООО "ФРЕШ-К"</t>
+          <t>АО "РОЛЬФ" ONLINE</t>
         </is>
       </c>
       <c r="F90" s="9" t="inlineStr">
@@ -6909,21 +6909,21 @@
         </is>
       </c>
       <c r="H90" s="12" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="I90" s="9" t="inlineStr">
         <is>
-          <t>JETOUR</t>
+          <t>Belgee</t>
         </is>
       </c>
       <c r="J90" s="9" t="inlineStr">
         <is>
-          <t>DASHING</t>
+          <t>BELGEE Х50+</t>
         </is>
       </c>
       <c r="K90" s="9" t="inlineStr">
         <is>
-          <t>EC3DLUFD2TC012452</t>
+          <t>Y4K8622Z4TB936627</t>
         </is>
       </c>
       <c r="L90" s="8" t="inlineStr">
@@ -6943,7 +6943,7 @@
       </c>
       <c r="O90" s="10" t="inlineStr">
         <is>
-          <t>https://back.sberauto.com/crm/leads/534986</t>
+          <t>https://back.sberauto.com/crm/leads/534742</t>
         </is>
       </c>
     </row>
@@ -6953,22 +6953,22 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>535468</t>
+          <t>536434</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>5116289</t>
+          <t>5174908</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>РОЛЬФ</t>
+          <t>АвтоГермес</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
         <is>
-          <t>АО "РОЛЬФ" ONLINE</t>
+          <t>ONLINE АВТОГЕРМЕС-ЗАПАД (ООО "АВТОГЕРМЕС-ЗАПАД")</t>
         </is>
       </c>
       <c r="F91" s="5" t="inlineStr">
@@ -6978,25 +6978,25 @@
       </c>
       <c r="G91" s="4" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>01.09.2026</t>
         </is>
       </c>
       <c r="H91" s="12" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="I91" s="5" t="inlineStr">
         <is>
-          <t>Geely</t>
+          <t>JETOUR</t>
         </is>
       </c>
       <c r="J91" s="5" t="inlineStr">
         <is>
-          <t>GEELY CITYRAY</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="K91" s="5" t="inlineStr">
         <is>
-          <t>LB3G43S96TX415101</t>
+          <t>LVTDD24B9TDC03464</t>
         </is>
       </c>
       <c r="L91" s="4" t="inlineStr">
@@ -7016,7 +7016,7 @@
       </c>
       <c r="O91" s="7" t="inlineStr">
         <is>
-          <t>https://back.sberauto.com/crm/leads/535468</t>
+          <t>https://back.sberauto.com/crm/leads/536434</t>
         </is>
       </c>
     </row>
@@ -7026,50 +7026,50 @@
       </c>
       <c r="B92" s="8" t="inlineStr">
         <is>
-          <t>535440</t>
+          <t>536162</t>
         </is>
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t>5166372</t>
+          <t>4191385</t>
         </is>
       </c>
       <c r="D92" s="9" t="inlineStr">
         <is>
-          <t>РОЛЬФ</t>
+          <t>ГК Major/Мэйджор</t>
         </is>
       </c>
       <c r="E92" s="9" t="inlineStr">
         <is>
-          <t>АО "РОЛЬФ" ONLINE</t>
+          <t>ONLINE ООО "МЭЙДЖОР АВТО КОМПЛЕКС"</t>
         </is>
       </c>
       <c r="F92" s="9" t="inlineStr">
         <is>
-          <t>Андрей Кузнецов</t>
+          <t>Алексей Чихарев</t>
         </is>
       </c>
       <c r="G92" s="8" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>01.09.2026</t>
         </is>
       </c>
       <c r="H92" s="12" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="I92" s="9" t="inlineStr">
         <is>
-          <t>JELAND</t>
+          <t>GAC</t>
         </is>
       </c>
       <c r="J92" s="9" t="inlineStr">
         <is>
-          <t>J6 AWD</t>
+          <t>GS8</t>
         </is>
       </c>
       <c r="K92" s="9" t="inlineStr">
         <is>
-          <t>EDXDD21B2TG031200</t>
+          <t>LMGJU3G86T1064025</t>
         </is>
       </c>
       <c r="L92" s="8" t="inlineStr">
@@ -7089,7 +7089,7 @@
       </c>
       <c r="O92" s="10" t="inlineStr">
         <is>
-          <t>https://back.sberauto.com/crm/leads/535440</t>
+          <t>https://back.sberauto.com/crm/leads/536162</t>
         </is>
       </c>
     </row>
@@ -7099,22 +7099,22 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>534742</t>
+          <t>529940</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>1232677</t>
+          <t>5129589</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>РОЛЬФ</t>
+          <t>АвтоГермес</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
         <is>
-          <t>АО "РОЛЬФ" ONLINE</t>
+          <t>ONLINE АВТОГЕРМЕС-ЗАПАД (ООО "АВТОГЕРМЕС-ЗАПАД")</t>
         </is>
       </c>
       <c r="F93" s="5" t="inlineStr">
@@ -7124,25 +7124,25 @@
       </c>
       <c r="G93" s="4" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>02.09.2026</t>
         </is>
       </c>
       <c r="H93" s="12" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I93" s="5" t="inlineStr">
         <is>
-          <t>Belgee</t>
+          <t>SOLARIS</t>
         </is>
       </c>
       <c r="J93" s="5" t="inlineStr">
         <is>
-          <t>BELGEE Х50+</t>
+          <t>НС</t>
         </is>
       </c>
       <c r="K93" s="5" t="inlineStr">
         <is>
-          <t>Y4K8622Z4TB936627</t>
+          <t>Z94PC815DSR074261</t>
         </is>
       </c>
       <c r="L93" s="4" t="inlineStr">
@@ -7162,7 +7162,7 @@
       </c>
       <c r="O93" s="7" t="inlineStr">
         <is>
-          <t>https://back.sberauto.com/crm/leads/534742</t>
+          <t>https://back.sberauto.com/crm/leads/529940</t>
         </is>
       </c>
     </row>
@@ -7172,22 +7172,22 @@
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>536434</t>
+          <t>537762</t>
         </is>
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
-          <t>5174908</t>
+          <t>5185604</t>
         </is>
       </c>
       <c r="D94" s="9" t="inlineStr">
         <is>
-          <t>АвтоГермес</t>
+          <t>ГК Автомир</t>
         </is>
       </c>
       <c r="E94" s="9" t="inlineStr">
         <is>
-          <t>ONLINE АВТОГЕРМЕС-ЗАПАД (ООО "АВТОГЕРМЕС-ЗАПАД")</t>
+          <t>ООО "АВТОМИР-ТРЕЙД" online</t>
         </is>
       </c>
       <c r="F94" s="9" t="inlineStr">
@@ -7197,25 +7197,25 @@
       </c>
       <c r="G94" s="8" t="inlineStr">
         <is>
-          <t>01.09.2026</t>
+          <t>02.09.2026</t>
         </is>
       </c>
       <c r="H94" s="12" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="I94" s="9" t="inlineStr">
         <is>
-          <t>JETOUR</t>
+          <t>Geely</t>
         </is>
       </c>
       <c r="J94" s="9" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>GEELY EX5</t>
         </is>
       </c>
       <c r="K94" s="9" t="inlineStr">
         <is>
-          <t>LVTDD24B9TDC03464</t>
+          <t>LB3P11SN6TH386266</t>
         </is>
       </c>
       <c r="L94" s="8" t="inlineStr">
@@ -7235,7 +7235,7 @@
       </c>
       <c r="O94" s="10" t="inlineStr">
         <is>
-          <t>https://back.sberauto.com/crm/leads/536434</t>
+          <t>https://back.sberauto.com/crm/leads/537762</t>
         </is>
       </c>
     </row>
@@ -7245,50 +7245,50 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>536162</t>
+          <t>537774</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>4191385</t>
+          <t>5186653</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>ГК Major/Мэйджор</t>
+          <t>ГК Арконт</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
         <is>
-          <t>ONLINE ООО "МЭЙДЖОР АВТО КОМПЛЕКС"</t>
+          <t>Online ООО "АРКОНТ В"</t>
         </is>
       </c>
       <c r="F95" s="5" t="inlineStr">
         <is>
-          <t>Алексей Чихарев</t>
+          <t>Евгения Добролюбова</t>
         </is>
       </c>
       <c r="G95" s="4" t="inlineStr">
         <is>
-          <t>01.09.2026</t>
+          <t>02.09.2026</t>
         </is>
       </c>
       <c r="H95" s="12" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="I95" s="5" t="inlineStr">
         <is>
-          <t>GAC</t>
+          <t>JETOUR</t>
         </is>
       </c>
       <c r="J95" s="5" t="inlineStr">
         <is>
-          <t>GS8</t>
+          <t>DASHING</t>
         </is>
       </c>
       <c r="K95" s="5" t="inlineStr">
         <is>
-          <t>LMGJU3G86T1064025</t>
+          <t>EC3DCUFD7SC008279</t>
         </is>
       </c>
       <c r="L95" s="4" t="inlineStr">
@@ -7308,7 +7308,7 @@
       </c>
       <c r="O95" s="7" t="inlineStr">
         <is>
-          <t>https://back.sberauto.com/crm/leads/536162</t>
+          <t>https://back.sberauto.com/crm/leads/537774</t>
         </is>
       </c>
     </row>
@@ -7318,22 +7318,22 @@
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
-          <t>529940</t>
+          <t>538554</t>
         </is>
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t>5129589</t>
+          <t>5196201</t>
         </is>
       </c>
       <c r="D96" s="9" t="inlineStr">
         <is>
-          <t>АвтоГермес</t>
+          <t>РОЛЬФ</t>
         </is>
       </c>
       <c r="E96" s="9" t="inlineStr">
         <is>
-          <t>ONLINE АВТОГЕРМЕС-ЗАПАД (ООО "АВТОГЕРМЕС-ЗАПАД")</t>
+          <t>АО "РОЛЬФ" ONLINE</t>
         </is>
       </c>
       <c r="F96" s="9" t="inlineStr">
@@ -7343,25 +7343,25 @@
       </c>
       <c r="G96" s="8" t="inlineStr">
         <is>
-          <t>02.09.2026</t>
+          <t>03.09.2026</t>
         </is>
       </c>
       <c r="H96" s="12" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="I96" s="9" t="inlineStr">
         <is>
-          <t>SOLARIS</t>
+          <t>Geely</t>
         </is>
       </c>
       <c r="J96" s="9" t="inlineStr">
         <is>
-          <t>НС</t>
+          <t>GEELY OKAVANGO</t>
         </is>
       </c>
       <c r="K96" s="9" t="inlineStr">
         <is>
-          <t>Z94PC815DSR074261</t>
+          <t>L6TVX1S66TY900885</t>
         </is>
       </c>
       <c r="L96" s="8" t="inlineStr">
@@ -7381,7 +7381,7 @@
       </c>
       <c r="O96" s="10" t="inlineStr">
         <is>
-          <t>https://back.sberauto.com/crm/leads/529940</t>
+          <t>https://back.sberauto.com/crm/leads/538554</t>
         </is>
       </c>
     </row>
@@ -7391,22 +7391,22 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>537762</t>
+          <t>539252</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>5185604</t>
+          <t>2346801</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>ГК Автомир</t>
+          <t>ГК АГАТ</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
         <is>
-          <t>ООО "АВТОМИР-ТРЕЙД" online</t>
+          <t>ГК АГАТ/ ООО "СПЕКТР" Online</t>
         </is>
       </c>
       <c r="F97" s="5" t="inlineStr">
@@ -7416,35 +7416,35 @@
       </c>
       <c r="G97" s="4" t="inlineStr">
         <is>
-          <t>02.09.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
       <c r="H97" s="12" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I97" s="5" t="inlineStr">
         <is>
-          <t>Geely</t>
+          <t>JETOUR</t>
         </is>
       </c>
       <c r="J97" s="5" t="inlineStr">
         <is>
-          <t>GEELY EX5</t>
+          <t>X70 PLUS</t>
         </is>
       </c>
       <c r="K97" s="5" t="inlineStr">
         <is>
-          <t>LB3P11SN6TH386266</t>
+          <t>539252</t>
         </is>
       </c>
       <c r="L97" s="4" t="inlineStr">
         <is>
-          <t>МП2</t>
+          <t>Online</t>
         </is>
       </c>
       <c r="M97" s="5" t="inlineStr">
         <is>
-          <t>Фокин Борис</t>
+          <t>Горбунов Роман</t>
         </is>
       </c>
       <c r="N97" s="5" t="inlineStr">
@@ -7454,7 +7454,7 @@
       </c>
       <c r="O97" s="7" t="inlineStr">
         <is>
-          <t>https://back.sberauto.com/crm/leads/537762</t>
+          <t>https://back.sberauto.com/crm/leads/539252</t>
         </is>
       </c>
     </row>
@@ -7464,22 +7464,22 @@
       </c>
       <c r="B98" s="8" t="inlineStr">
         <is>
-          <t>537774</t>
+          <t>539412</t>
         </is>
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t>5186653</t>
+          <t>2371109</t>
         </is>
       </c>
       <c r="D98" s="9" t="inlineStr">
         <is>
-          <t>ГК Арконт</t>
+          <t>ЮНИКОР Дзержинск НН</t>
         </is>
       </c>
       <c r="E98" s="9" t="inlineStr">
         <is>
-          <t>Online ООО "АРКОНТ В"</t>
+          <t>ONLINE ЮНИКОР (ООО "ЮНИКОР")</t>
         </is>
       </c>
       <c r="F98" s="9" t="inlineStr">
@@ -7489,25 +7489,25 @@
       </c>
       <c r="G98" s="8" t="inlineStr">
         <is>
-          <t>02.09.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
       <c r="H98" s="12" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I98" s="9" t="inlineStr">
         <is>
-          <t>JETOUR</t>
+          <t>LADA</t>
         </is>
       </c>
       <c r="J98" s="9" t="inlineStr">
         <is>
-          <t>DASHING</t>
+          <t>GRANTA</t>
         </is>
       </c>
       <c r="K98" s="9" t="inlineStr">
         <is>
-          <t>EC3DCUFD7SC008279</t>
+          <t>XTA219470V0325247</t>
         </is>
       </c>
       <c r="L98" s="8" t="inlineStr">
@@ -7527,7 +7527,7 @@
       </c>
       <c r="O98" s="10" t="inlineStr">
         <is>
-          <t>https://back.sberauto.com/crm/leads/537774</t>
+          <t>https://back.sberauto.com/crm/leads/539412</t>
         </is>
       </c>
     </row>
@@ -7537,70 +7537,1384 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>538554</t>
+          <t>540110</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>5196201</t>
+          <t>5212250</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
+          <t>АвтоДом Петрозаводск</t>
+        </is>
+      </c>
+      <c r="E99" s="5" t="inlineStr">
+        <is>
+          <t>АО "АВТОДОМ" online</t>
+        </is>
+      </c>
+      <c r="F99" s="5" t="inlineStr">
+        <is>
+          <t>Алексей Чихарев</t>
+        </is>
+      </c>
+      <c r="G99" s="4" t="inlineStr">
+        <is>
+          <t>05.09.2026</t>
+        </is>
+      </c>
+      <c r="H99" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="I99" s="5" t="inlineStr">
+        <is>
+          <t>SOLARIS</t>
+        </is>
+      </c>
+      <c r="J99" s="5" t="inlineStr">
+        <is>
+          <t>KRX</t>
+        </is>
+      </c>
+      <c r="K99" s="5" t="inlineStr">
+        <is>
+          <t>Z94C351BBSR199664</t>
+        </is>
+      </c>
+      <c r="L99" s="4" t="inlineStr">
+        <is>
+          <t>МП2</t>
+        </is>
+      </c>
+      <c r="M99" s="5" t="inlineStr">
+        <is>
+          <t>Фокин Борис</t>
+        </is>
+      </c>
+      <c r="N99" s="5" t="inlineStr">
+        <is>
+          <t>ПРЕДДКП ОПЛАЧЕН</t>
+        </is>
+      </c>
+      <c r="O99" s="7" t="inlineStr">
+        <is>
+          <t>https://back.sberauto.com/crm/leads/540110</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="22" customHeight="1">
+      <c r="A100" s="8" t="n">
+        <v>96</v>
+      </c>
+      <c r="B100" s="8" t="inlineStr">
+        <is>
+          <t>540340</t>
+        </is>
+      </c>
+      <c r="C100" s="8" t="inlineStr">
+        <is>
+          <t>5203489</t>
+        </is>
+      </c>
+      <c r="D100" s="9" t="inlineStr">
+        <is>
+          <t>ГК КОРС Джетур</t>
+        </is>
+      </c>
+      <c r="E100" s="9" t="inlineStr">
+        <is>
+          <t>ООО "КОРС НОВОМОСКОВСК" ONLINE</t>
+        </is>
+      </c>
+      <c r="F100" s="9" t="inlineStr">
+        <is>
+          <t>Андрей Кузнецов</t>
+        </is>
+      </c>
+      <c r="G100" s="8" t="inlineStr">
+        <is>
+          <t>05.09.2026</t>
+        </is>
+      </c>
+      <c r="H100" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="I100" s="9" t="inlineStr">
+        <is>
+          <t>SOUEAST</t>
+        </is>
+      </c>
+      <c r="J100" s="9" t="inlineStr">
+        <is>
+          <t>S06</t>
+        </is>
+      </c>
+      <c r="K100" s="9" t="inlineStr">
+        <is>
+          <t>EC3DCUGA5TC000901</t>
+        </is>
+      </c>
+      <c r="L100" s="8" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="M100" s="9" t="inlineStr">
+        <is>
+          <t>Горбунов Роман</t>
+        </is>
+      </c>
+      <c r="N100" s="9" t="inlineStr">
+        <is>
+          <t>ПРЕДДКП ОПЛАЧЕН</t>
+        </is>
+      </c>
+      <c r="O100" s="10" t="inlineStr">
+        <is>
+          <t>https://back.sberauto.com/crm/leads/540340</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="22" customHeight="1">
+      <c r="A101" s="4" t="n">
+        <v>97</v>
+      </c>
+      <c r="B101" s="4" t="inlineStr">
+        <is>
+          <t>539902</t>
+        </is>
+      </c>
+      <c r="C101" s="4" t="inlineStr">
+        <is>
+          <t>4736114</t>
+        </is>
+      </c>
+      <c r="D101" s="5" t="inlineStr">
+        <is>
+          <t>ТСАЦ Июль</t>
+        </is>
+      </c>
+      <c r="E101" s="5" t="inlineStr">
+        <is>
+          <t>ONLINE O&amp;J Июль (ООО "НАШИ МАШИНЫ")</t>
+        </is>
+      </c>
+      <c r="F101" s="5" t="inlineStr">
+        <is>
+          <t>Евгения Добролюбова</t>
+        </is>
+      </c>
+      <c r="G101" s="4" t="inlineStr">
+        <is>
+          <t>05.09.2026</t>
+        </is>
+      </c>
+      <c r="H101" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="I101" s="5" t="inlineStr">
+        <is>
+          <t>JELAND</t>
+        </is>
+      </c>
+      <c r="J101" s="5" t="inlineStr">
+        <is>
+          <t>JAECOO J6</t>
+        </is>
+      </c>
+      <c r="K101" s="5" t="inlineStr">
+        <is>
+          <t>EDXDD21B3TG032596</t>
+        </is>
+      </c>
+      <c r="L101" s="4" t="inlineStr">
+        <is>
+          <t>ФДЦ</t>
+        </is>
+      </c>
+      <c r="M101" s="5" t="inlineStr">
+        <is>
+          <t>Григорян Михаил</t>
+        </is>
+      </c>
+      <c r="N101" s="5" t="inlineStr">
+        <is>
+          <t>ПРЕДДКП ОПЛАЧЕН</t>
+        </is>
+      </c>
+      <c r="O101" s="7" t="inlineStr">
+        <is>
+          <t>https://back.sberauto.com/crm/leads/539902</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="22" customHeight="1">
+      <c r="A102" s="8" t="n">
+        <v>98</v>
+      </c>
+      <c r="B102" s="8" t="inlineStr">
+        <is>
+          <t>540850</t>
+        </is>
+      </c>
+      <c r="C102" s="8" t="inlineStr">
+        <is>
+          <t>5219355</t>
+        </is>
+      </c>
+      <c r="D102" s="9" t="inlineStr">
+        <is>
+          <t>Автохолдинг Максимум</t>
+        </is>
+      </c>
+      <c r="E102" s="9" t="inlineStr">
+        <is>
+          <t>ООО "МАКСИМУМ КРЕДИТ" online</t>
+        </is>
+      </c>
+      <c r="F102" s="9" t="inlineStr">
+        <is>
+          <t>Светлана Дариенко</t>
+        </is>
+      </c>
+      <c r="G102" s="8" t="inlineStr">
+        <is>
+          <t>06.09.2026</t>
+        </is>
+      </c>
+      <c r="H102" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="I102" s="9" t="inlineStr">
+        <is>
+          <t>JETOUR</t>
+        </is>
+      </c>
+      <c r="J102" s="9" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="K102" s="9" t="inlineStr">
+        <is>
+          <t>LVTDD24B7TDB98779</t>
+        </is>
+      </c>
+      <c r="L102" s="8" t="inlineStr">
+        <is>
+          <t>МП2</t>
+        </is>
+      </c>
+      <c r="M102" s="9" t="inlineStr">
+        <is>
+          <t>Фокин Борис</t>
+        </is>
+      </c>
+      <c r="N102" s="9" t="inlineStr">
+        <is>
+          <t>ПРЕДДКП ОПЛАЧЕН</t>
+        </is>
+      </c>
+      <c r="O102" s="10" t="inlineStr">
+        <is>
+          <t>https://back.sberauto.com/crm/leads/540850</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="22" customHeight="1">
+      <c r="A103" s="4" t="n">
+        <v>99</v>
+      </c>
+      <c r="B103" s="4" t="inlineStr">
+        <is>
+          <t>541134</t>
+        </is>
+      </c>
+      <c r="C103" s="4" t="inlineStr">
+        <is>
+          <t>5221891</t>
+        </is>
+      </c>
+      <c r="D103" s="5" t="inlineStr">
+        <is>
+          <t>ГК АГАТ</t>
+        </is>
+      </c>
+      <c r="E103" s="5" t="inlineStr">
+        <is>
+          <t>ГК АГАТ/ ООО "СПЕКТР" Online</t>
+        </is>
+      </c>
+      <c r="F103" s="5" t="inlineStr">
+        <is>
+          <t>Андрей Кузнецов</t>
+        </is>
+      </c>
+      <c r="G103" s="4" t="inlineStr">
+        <is>
+          <t>06.09.2026</t>
+        </is>
+      </c>
+      <c r="H103" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="I103" s="5" t="inlineStr">
+        <is>
+          <t>SOUEAST</t>
+        </is>
+      </c>
+      <c r="J103" s="5" t="inlineStr">
+        <is>
+          <t>S06</t>
+        </is>
+      </c>
+      <c r="K103" s="5" t="inlineStr">
+        <is>
+          <t>EC3DCUGA1TC000796</t>
+        </is>
+      </c>
+      <c r="L103" s="4" t="inlineStr">
+        <is>
+          <t>МП2</t>
+        </is>
+      </c>
+      <c r="M103" s="5" t="inlineStr">
+        <is>
+          <t>Фокин Борис</t>
+        </is>
+      </c>
+      <c r="N103" s="5" t="inlineStr">
+        <is>
+          <t>ПРЕДДКП ОПЛАЧЕН</t>
+        </is>
+      </c>
+      <c r="O103" s="7" t="inlineStr">
+        <is>
+          <t>https://back.sberauto.com/crm/leads/541134</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="22" customHeight="1">
+      <c r="A104" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B104" s="8" t="inlineStr">
+        <is>
+          <t>541052</t>
+        </is>
+      </c>
+      <c r="C104" s="8" t="inlineStr">
+        <is>
+          <t>5221247</t>
+        </is>
+      </c>
+      <c r="D104" s="9" t="inlineStr">
+        <is>
+          <t>ЗВЕЗДА ЯРОСЛАВИИ</t>
+        </is>
+      </c>
+      <c r="E104" s="9" t="inlineStr">
+        <is>
+          <t>ООО "ЗВЕЗДА ЯРОСЛАВИИ" Online</t>
+        </is>
+      </c>
+      <c r="F104" s="9" t="inlineStr">
+        <is>
+          <t>Алексей Чихарев</t>
+        </is>
+      </c>
+      <c r="G104" s="8" t="inlineStr">
+        <is>
+          <t>06.09.2026</t>
+        </is>
+      </c>
+      <c r="H104" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="I104" s="9" t="inlineStr">
+        <is>
+          <t>JETOUR</t>
+        </is>
+      </c>
+      <c r="J104" s="9" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="K104" s="9" t="inlineStr">
+        <is>
+          <t>LVTDD24B8TDB98807</t>
+        </is>
+      </c>
+      <c r="L104" s="8" t="inlineStr">
+        <is>
+          <t>МП2</t>
+        </is>
+      </c>
+      <c r="M104" s="9" t="inlineStr">
+        <is>
+          <t>Фокин Борис</t>
+        </is>
+      </c>
+      <c r="N104" s="9" t="inlineStr">
+        <is>
+          <t>ПРЕДДКП ОПЛАЧЕН</t>
+        </is>
+      </c>
+      <c r="O104" s="10" t="inlineStr">
+        <is>
+          <t>https://back.sberauto.com/crm/leads/541052</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="22" customHeight="1">
+      <c r="A105" s="4" t="n">
+        <v>101</v>
+      </c>
+      <c r="B105" s="4" t="inlineStr">
+        <is>
+          <t>541544</t>
+        </is>
+      </c>
+      <c r="C105" s="4" t="inlineStr">
+        <is>
+          <t>4942705</t>
+        </is>
+      </c>
+      <c r="D105" s="5" t="inlineStr">
+        <is>
+          <t>Прагматика</t>
+        </is>
+      </c>
+      <c r="E105" s="5" t="inlineStr">
+        <is>
+          <t>Прагматика Лада Великий Новгород (ООО "НОВГОРОД-ЛАДА) ONLINE</t>
+        </is>
+      </c>
+      <c r="F105" s="5" t="inlineStr">
+        <is>
+          <t>Светлана Дариенко</t>
+        </is>
+      </c>
+      <c r="G105" s="4" t="inlineStr">
+        <is>
+          <t>06.09.2026</t>
+        </is>
+      </c>
+      <c r="H105" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="I105" s="5" t="inlineStr">
+        <is>
+          <t>LADA</t>
+        </is>
+      </c>
+      <c r="J105" s="5" t="inlineStr">
+        <is>
+          <t>ISKRA</t>
+        </is>
+      </c>
+      <c r="K105" s="5" t="inlineStr">
+        <is>
+          <t>541544</t>
+        </is>
+      </c>
+      <c r="L105" s="4" t="inlineStr">
+        <is>
+          <t>МП2</t>
+        </is>
+      </c>
+      <c r="M105" s="5" t="inlineStr">
+        <is>
+          <t>Горбунов Роман</t>
+        </is>
+      </c>
+      <c r="N105" s="5" t="inlineStr">
+        <is>
+          <t>ПРЕДДКП ОПЛАЧЕН</t>
+        </is>
+      </c>
+      <c r="O105" s="7" t="inlineStr">
+        <is>
+          <t>https://back.sberauto.com/crm/leads/541544</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="22" customHeight="1">
+      <c r="A106" s="8" t="n">
+        <v>102</v>
+      </c>
+      <c r="B106" s="8" t="inlineStr">
+        <is>
+          <t>542072</t>
+        </is>
+      </c>
+      <c r="C106" s="8" t="inlineStr">
+        <is>
+          <t>5215277</t>
+        </is>
+      </c>
+      <c r="D106" s="9" t="inlineStr">
+        <is>
+          <t>ТЦ Кунцево</t>
+        </is>
+      </c>
+      <c r="E106" s="9" t="inlineStr">
+        <is>
+          <t>ООО "ТЦ "КУНЦЕВО ЛИМИТЕД" ONLINE</t>
+        </is>
+      </c>
+      <c r="F106" s="9" t="inlineStr">
+        <is>
+          <t>Алексей Чихарев</t>
+        </is>
+      </c>
+      <c r="G106" s="8" t="inlineStr">
+        <is>
+          <t>06.09.2026</t>
+        </is>
+      </c>
+      <c r="H106" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="I106" s="9" t="inlineStr">
+        <is>
+          <t>GAC</t>
+        </is>
+      </c>
+      <c r="J106" s="9" t="inlineStr">
+        <is>
+          <t>S9</t>
+        </is>
+      </c>
+      <c r="K106" s="9" t="inlineStr">
+        <is>
+          <t>542072</t>
+        </is>
+      </c>
+      <c r="L106" s="8" t="inlineStr">
+        <is>
+          <t>ФДЦ</t>
+        </is>
+      </c>
+      <c r="M106" s="9" t="inlineStr">
+        <is>
+          <t>Вершинин Николай</t>
+        </is>
+      </c>
+      <c r="N106" s="9" t="inlineStr">
+        <is>
+          <t>ПРЕДДКП ОПЛАЧЕН</t>
+        </is>
+      </c>
+      <c r="O106" s="10" t="inlineStr">
+        <is>
+          <t>https://back.sberauto.com/crm/leads/542072</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="22" customHeight="1">
+      <c r="A107" s="4" t="n">
+        <v>103</v>
+      </c>
+      <c r="B107" s="4" t="inlineStr">
+        <is>
+          <t>540842</t>
+        </is>
+      </c>
+      <c r="C107" s="4" t="inlineStr">
+        <is>
+          <t>5215277</t>
+        </is>
+      </c>
+      <c r="D107" s="5" t="inlineStr">
+        <is>
+          <t>ТЦ Кунцево</t>
+        </is>
+      </c>
+      <c r="E107" s="5" t="inlineStr">
+        <is>
+          <t>ООО "ТЦ "КУНЦЕВО ЛИМИТЕД" ONLINE</t>
+        </is>
+      </c>
+      <c r="F107" s="5" t="inlineStr">
+        <is>
+          <t>Алексей Чихарев</t>
+        </is>
+      </c>
+      <c r="G107" s="4" t="inlineStr">
+        <is>
+          <t>06.09.2026</t>
+        </is>
+      </c>
+      <c r="H107" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="I107" s="5" t="inlineStr">
+        <is>
+          <t>GAC</t>
+        </is>
+      </c>
+      <c r="J107" s="5" t="inlineStr">
+        <is>
+          <t>S9</t>
+        </is>
+      </c>
+      <c r="K107" s="5" t="inlineStr">
+        <is>
+          <t>540842</t>
+        </is>
+      </c>
+      <c r="L107" s="4" t="inlineStr">
+        <is>
+          <t>ФДЦ</t>
+        </is>
+      </c>
+      <c r="M107" s="5" t="inlineStr">
+        <is>
+          <t>Красильников Станислав</t>
+        </is>
+      </c>
+      <c r="N107" s="5" t="inlineStr">
+        <is>
+          <t>ПРЕДДКП ОПЛАЧЕН</t>
+        </is>
+      </c>
+      <c r="O107" s="7" t="inlineStr">
+        <is>
+          <t>https://back.sberauto.com/crm/leads/540842</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="22" customHeight="1">
+      <c r="A108" s="8" t="n">
+        <v>104</v>
+      </c>
+      <c r="B108" s="8" t="inlineStr">
+        <is>
+          <t>541836</t>
+        </is>
+      </c>
+      <c r="C108" s="8" t="inlineStr">
+        <is>
+          <t>5228043</t>
+        </is>
+      </c>
+      <c r="D108" s="9" t="inlineStr">
+        <is>
+          <t>ГК Автомир</t>
+        </is>
+      </c>
+      <c r="E108" s="9" t="inlineStr">
+        <is>
+          <t>ONLINE ООО "АМКАПИТАЛ"</t>
+        </is>
+      </c>
+      <c r="F108" s="9" t="inlineStr">
+        <is>
+          <t>Андрей Кузнецов</t>
+        </is>
+      </c>
+      <c r="G108" s="8" t="inlineStr">
+        <is>
+          <t>07.09.2026</t>
+        </is>
+      </c>
+      <c r="H108" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="I108" s="9" t="inlineStr">
+        <is>
+          <t>JETOUR</t>
+        </is>
+      </c>
+      <c r="J108" s="9" t="inlineStr">
+        <is>
+          <t>DASHING</t>
+        </is>
+      </c>
+      <c r="K108" s="9" t="inlineStr">
+        <is>
+          <t>EC3DCUFD2TC016355</t>
+        </is>
+      </c>
+      <c r="L108" s="8" t="inlineStr">
+        <is>
+          <t>МП2</t>
+        </is>
+      </c>
+      <c r="M108" s="9" t="inlineStr">
+        <is>
+          <t>Фокин Борис</t>
+        </is>
+      </c>
+      <c r="N108" s="9" t="inlineStr">
+        <is>
+          <t>ПРЕДДКП ОПЛАЧЕН</t>
+        </is>
+      </c>
+      <c r="O108" s="10" t="inlineStr">
+        <is>
+          <t>https://back.sberauto.com/crm/leads/541836</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="22" customHeight="1">
+      <c r="A109" s="4" t="n">
+        <v>105</v>
+      </c>
+      <c r="B109" s="4" t="inlineStr">
+        <is>
+          <t>541844</t>
+        </is>
+      </c>
+      <c r="C109" s="4" t="inlineStr">
+        <is>
+          <t>5228130</t>
+        </is>
+      </c>
+      <c r="D109" s="5" t="inlineStr">
+        <is>
           <t>РОЛЬФ</t>
         </is>
       </c>
-      <c r="E99" s="5" t="inlineStr">
+      <c r="E109" s="5" t="inlineStr">
         <is>
           <t>АО "РОЛЬФ" ONLINE</t>
         </is>
       </c>
-      <c r="F99" s="5" t="inlineStr">
+      <c r="F109" s="5" t="inlineStr">
         <is>
           <t>Андрей Кузнецов</t>
         </is>
       </c>
-      <c r="G99" s="4" t="inlineStr">
-        <is>
-          <t>03.09.2026</t>
-        </is>
-      </c>
-      <c r="H99" s="12" t="n">
+      <c r="G109" s="4" t="inlineStr">
+        <is>
+          <t>07.09.2026</t>
+        </is>
+      </c>
+      <c r="H109" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="I109" s="5" t="inlineStr">
+        <is>
+          <t>Geely</t>
+        </is>
+      </c>
+      <c r="J109" s="5" t="inlineStr">
+        <is>
+          <t>GEELY MONJARO</t>
+        </is>
+      </c>
+      <c r="K109" s="5" t="inlineStr">
+        <is>
+          <t>LB37852D6TS081279</t>
+        </is>
+      </c>
+      <c r="L109" s="4" t="inlineStr">
+        <is>
+          <t>МП2</t>
+        </is>
+      </c>
+      <c r="M109" s="5" t="inlineStr">
+        <is>
+          <t>Фокин Борис</t>
+        </is>
+      </c>
+      <c r="N109" s="5" t="inlineStr">
+        <is>
+          <t>ПРЕДДКП ОПЛАЧЕН</t>
+        </is>
+      </c>
+      <c r="O109" s="7" t="inlineStr">
+        <is>
+          <t>https://back.sberauto.com/crm/leads/541844</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="22" customHeight="1">
+      <c r="A110" s="8" t="n">
+        <v>106</v>
+      </c>
+      <c r="B110" s="8" t="inlineStr">
+        <is>
+          <t>542020</t>
+        </is>
+      </c>
+      <c r="C110" s="8" t="inlineStr">
+        <is>
+          <t>5229376</t>
+        </is>
+      </c>
+      <c r="D110" s="9" t="inlineStr">
+        <is>
+          <t>ТЦ Кунцево</t>
+        </is>
+      </c>
+      <c r="E110" s="9" t="inlineStr">
+        <is>
+          <t>ООО "Кунцево Авто Трейдинг" (ООО "КУНЦЕВО АТ") Online</t>
+        </is>
+      </c>
+      <c r="F110" s="9" t="inlineStr">
+        <is>
+          <t>Алексей Чихарев</t>
+        </is>
+      </c>
+      <c r="G110" s="8" t="inlineStr">
+        <is>
+          <t>07.09.2026</t>
+        </is>
+      </c>
+      <c r="H110" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="I110" s="9" t="inlineStr">
+        <is>
+          <t>CHANGAN</t>
+        </is>
+      </c>
+      <c r="J110" s="9" t="inlineStr">
+        <is>
+          <t>CS35</t>
+        </is>
+      </c>
+      <c r="K110" s="9" t="inlineStr">
+        <is>
+          <t>542020</t>
+        </is>
+      </c>
+      <c r="L110" s="8" t="inlineStr">
+        <is>
+          <t>МП2</t>
+        </is>
+      </c>
+      <c r="M110" s="9" t="inlineStr">
+        <is>
+          <t>Фокин Борис</t>
+        </is>
+      </c>
+      <c r="N110" s="9" t="inlineStr">
+        <is>
+          <t>ПРЕДДКП ОПЛАЧЕН</t>
+        </is>
+      </c>
+      <c r="O110" s="10" t="inlineStr">
+        <is>
+          <t>https://back.sberauto.com/crm/leads/542020</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="22" customHeight="1">
+      <c r="A111" s="4" t="n">
+        <v>107</v>
+      </c>
+      <c r="B111" s="4" t="inlineStr">
+        <is>
+          <t>552170</t>
+        </is>
+      </c>
+      <c r="C111" s="4" t="inlineStr">
+        <is>
+          <t>5238800</t>
+        </is>
+      </c>
+      <c r="D111" s="5" t="inlineStr">
+        <is>
+          <t>АвтоГермес</t>
+        </is>
+      </c>
+      <c r="E111" s="5" t="inlineStr">
+        <is>
+          <t>ONLINE АВТОГЕРМЕС-ЗАПАД (ООО "АВТОГЕРМЕС-ЗАПАД")</t>
+        </is>
+      </c>
+      <c r="F111" s="5" t="inlineStr">
+        <is>
+          <t>Андрей Кузнецов</t>
+        </is>
+      </c>
+      <c r="G111" s="4" t="inlineStr">
+        <is>
+          <t>08.09.2026</t>
+        </is>
+      </c>
+      <c r="H111" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="I111" s="5" t="inlineStr">
+        <is>
+          <t>JETOUR</t>
+        </is>
+      </c>
+      <c r="J111" s="5" t="inlineStr">
+        <is>
+          <t>DASHING</t>
+        </is>
+      </c>
+      <c r="K111" s="5" t="inlineStr">
+        <is>
+          <t>EC3DLUFD3TC016784</t>
+        </is>
+      </c>
+      <c r="L111" s="4" t="inlineStr">
+        <is>
+          <t>МП2</t>
+        </is>
+      </c>
+      <c r="M111" s="5" t="inlineStr">
+        <is>
+          <t>Фокин Борис</t>
+        </is>
+      </c>
+      <c r="N111" s="5" t="inlineStr">
+        <is>
+          <t>ПРЕДДКП ОПЛАЧЕН</t>
+        </is>
+      </c>
+      <c r="O111" s="7" t="inlineStr">
+        <is>
+          <t>https://back.sberauto.com/crm/leads/552170</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="22" customHeight="1">
+      <c r="A112" s="8" t="n">
+        <v>108</v>
+      </c>
+      <c r="B112" s="8" t="inlineStr">
+        <is>
+          <t>551824</t>
+        </is>
+      </c>
+      <c r="C112" s="8" t="inlineStr">
+        <is>
+          <t>5236540</t>
+        </is>
+      </c>
+      <c r="D112" s="9" t="inlineStr">
+        <is>
+          <t>АвтоГермес</t>
+        </is>
+      </c>
+      <c r="E112" s="9" t="inlineStr">
+        <is>
+          <t>ONLINE АВТОГЕРМЕС-ЗАПАД (ООО "АВТОГЕРМЕС-ЗАПАД")</t>
+        </is>
+      </c>
+      <c r="F112" s="9" t="inlineStr">
+        <is>
+          <t>Андрей Кузнецов</t>
+        </is>
+      </c>
+      <c r="G112" s="8" t="inlineStr">
+        <is>
+          <t>08.09.2026</t>
+        </is>
+      </c>
+      <c r="H112" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="I112" s="9" t="inlineStr">
+        <is>
+          <t>JETOUR</t>
+        </is>
+      </c>
+      <c r="J112" s="9" t="inlineStr">
+        <is>
+          <t>DASHING</t>
+        </is>
+      </c>
+      <c r="K112" s="9" t="inlineStr">
+        <is>
+          <t>EC3DLUFD7TC012852</t>
+        </is>
+      </c>
+      <c r="L112" s="8" t="inlineStr">
+        <is>
+          <t>МП2</t>
+        </is>
+      </c>
+      <c r="M112" s="9" t="inlineStr">
+        <is>
+          <t>Фокин Борис</t>
+        </is>
+      </c>
+      <c r="N112" s="9" t="inlineStr">
+        <is>
+          <t>ПРЕДДКП ОПЛАЧЕН</t>
+        </is>
+      </c>
+      <c r="O112" s="10" t="inlineStr">
+        <is>
+          <t>https://back.sberauto.com/crm/leads/551824</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="22" customHeight="1">
+      <c r="A113" s="4" t="n">
+        <v>109</v>
+      </c>
+      <c r="B113" s="4" t="inlineStr">
+        <is>
+          <t>550252</t>
+        </is>
+      </c>
+      <c r="C113" s="4" t="inlineStr">
+        <is>
+          <t>5236240</t>
+        </is>
+      </c>
+      <c r="D113" s="5" t="inlineStr">
+        <is>
+          <t>АвтоГермес</t>
+        </is>
+      </c>
+      <c r="E113" s="5" t="inlineStr">
+        <is>
+          <t>ONLINE АВТОГЕРМЕС-ЗАПАД (ООО "АВТОГЕРМЕС-ЗАПАД")</t>
+        </is>
+      </c>
+      <c r="F113" s="5" t="inlineStr">
+        <is>
+          <t>Андрей Кузнецов</t>
+        </is>
+      </c>
+      <c r="G113" s="4" t="inlineStr">
+        <is>
+          <t>08.09.2026</t>
+        </is>
+      </c>
+      <c r="H113" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="I113" s="5" t="inlineStr">
+        <is>
+          <t>LADA</t>
+        </is>
+      </c>
+      <c r="J113" s="5" t="inlineStr">
+        <is>
+          <t>GRANTA</t>
+        </is>
+      </c>
+      <c r="K113" s="5" t="inlineStr">
+        <is>
+          <t>XTA219440V0324895</t>
+        </is>
+      </c>
+      <c r="L113" s="4" t="inlineStr">
+        <is>
+          <t>МП2</t>
+        </is>
+      </c>
+      <c r="M113" s="5" t="inlineStr">
+        <is>
+          <t>Фокин Борис</t>
+        </is>
+      </c>
+      <c r="N113" s="5" t="inlineStr">
+        <is>
+          <t>ПРЕДДКП ОПЛАЧЕН</t>
+        </is>
+      </c>
+      <c r="O113" s="7" t="inlineStr">
+        <is>
+          <t>https://back.sberauto.com/crm/leads/550252</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="22" customHeight="1">
+      <c r="A114" s="8" t="n">
+        <v>110</v>
+      </c>
+      <c r="B114" s="8" t="inlineStr">
+        <is>
+          <t>552104</t>
+        </is>
+      </c>
+      <c r="C114" s="8" t="inlineStr">
+        <is>
+          <t>5238183</t>
+        </is>
+      </c>
+      <c r="D114" s="9" t="inlineStr">
+        <is>
+          <t>ГК Автомир</t>
+        </is>
+      </c>
+      <c r="E114" s="9" t="inlineStr">
+        <is>
+          <t>ООО "АВТОМИР-ТРЕЙД" online</t>
+        </is>
+      </c>
+      <c r="F114" s="9" t="inlineStr">
+        <is>
+          <t>Андрей Кузнецов</t>
+        </is>
+      </c>
+      <c r="G114" s="8" t="inlineStr">
+        <is>
+          <t>08.09.2026</t>
+        </is>
+      </c>
+      <c r="H114" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="I114" s="9" t="inlineStr">
+        <is>
+          <t>Belgee</t>
+        </is>
+      </c>
+      <c r="J114" s="9" t="inlineStr">
+        <is>
+          <t>BELGEE X50+</t>
+        </is>
+      </c>
+      <c r="K114" s="9" t="inlineStr">
+        <is>
+          <t>Y4K8622Z8TB934198</t>
+        </is>
+      </c>
+      <c r="L114" s="8" t="inlineStr">
+        <is>
+          <t>МП2</t>
+        </is>
+      </c>
+      <c r="M114" s="9" t="inlineStr">
+        <is>
+          <t>Фокин Борис</t>
+        </is>
+      </c>
+      <c r="N114" s="9" t="inlineStr">
+        <is>
+          <t>ПРЕДДКП ОПЛАЧЕН</t>
+        </is>
+      </c>
+      <c r="O114" s="10" t="inlineStr">
+        <is>
+          <t>https://back.sberauto.com/crm/leads/552104</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="22" customHeight="1">
+      <c r="A115" s="4" t="n">
+        <v>111</v>
+      </c>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
+          <t>551842</t>
+        </is>
+      </c>
+      <c r="C115" s="4" t="inlineStr">
+        <is>
+          <t>5237331</t>
+        </is>
+      </c>
+      <c r="D115" s="5" t="inlineStr">
+        <is>
+          <t>ООО "ТД АРМАДА-АВТО</t>
+        </is>
+      </c>
+      <c r="E115" s="5" t="inlineStr">
+        <is>
+          <t>ONLINE ООО "ТД АРМАДА-АВТО"</t>
+        </is>
+      </c>
+      <c r="F115" s="5" t="inlineStr">
+        <is>
+          <t>Евгения Добролюбова</t>
+        </is>
+      </c>
+      <c r="G115" s="4" t="inlineStr">
+        <is>
+          <t>08.09.2026</t>
+        </is>
+      </c>
+      <c r="H115" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="I115" s="5" t="inlineStr">
+        <is>
+          <t>JETOUR</t>
+        </is>
+      </c>
+      <c r="J115" s="5" t="inlineStr">
+        <is>
+          <t>DASHING</t>
+        </is>
+      </c>
+      <c r="K115" s="5" t="inlineStr">
+        <is>
+          <t>EC3DCUFD6TC010848</t>
+        </is>
+      </c>
+      <c r="L115" s="4" t="inlineStr">
+        <is>
+          <t>МП2</t>
+        </is>
+      </c>
+      <c r="M115" s="5" t="inlineStr">
+        <is>
+          <t>Фокин Борис</t>
+        </is>
+      </c>
+      <c r="N115" s="5" t="inlineStr">
+        <is>
+          <t>ПРЕДДКП ОПЛАЧЕН</t>
+        </is>
+      </c>
+      <c r="O115" s="7" t="inlineStr">
+        <is>
+          <t>https://back.sberauto.com/crm/leads/551842</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="22" customHeight="1">
+      <c r="A116" s="8" t="n">
+        <v>112</v>
+      </c>
+      <c r="B116" s="8" t="inlineStr">
+        <is>
+          <t>552038</t>
+        </is>
+      </c>
+      <c r="C116" s="8" t="inlineStr">
+        <is>
+          <t>5237926</t>
+        </is>
+      </c>
+      <c r="D116" s="9" t="inlineStr">
+        <is>
+          <t>РОЛЬФ</t>
+        </is>
+      </c>
+      <c r="E116" s="9" t="inlineStr">
+        <is>
+          <t>АО "РОЛЬФ" ONLINE</t>
+        </is>
+      </c>
+      <c r="F116" s="9" t="inlineStr">
+        <is>
+          <t>Андрей Кузнецов</t>
+        </is>
+      </c>
+      <c r="G116" s="8" t="inlineStr">
+        <is>
+          <t>08.09.2026</t>
+        </is>
+      </c>
+      <c r="H116" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="I116" s="9" t="inlineStr">
+        <is>
+          <t>Geely</t>
+        </is>
+      </c>
+      <c r="J116" s="9" t="inlineStr">
+        <is>
+          <t>GEELY EX-5</t>
+        </is>
+      </c>
+      <c r="K116" s="9" t="inlineStr">
+        <is>
+          <t>LB3P11SN5TH392642</t>
+        </is>
+      </c>
+      <c r="L116" s="8" t="inlineStr">
+        <is>
+          <t>МП2</t>
+        </is>
+      </c>
+      <c r="M116" s="9" t="inlineStr">
+        <is>
+          <t>Фокин Борис</t>
+        </is>
+      </c>
+      <c r="N116" s="9" t="inlineStr">
+        <is>
+          <t>ПРЕДДКП ОПЛАЧЕН</t>
+        </is>
+      </c>
+      <c r="O116" s="10" t="inlineStr">
+        <is>
+          <t>https://back.sberauto.com/crm/leads/552038</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="22" customHeight="1">
+      <c r="A117" s="4" t="n">
+        <v>113</v>
+      </c>
+      <c r="B117" s="4" t="inlineStr">
+        <is>
+          <t>552786</t>
+        </is>
+      </c>
+      <c r="C117" s="4" t="inlineStr">
+        <is>
+          <t>5246973</t>
+        </is>
+      </c>
+      <c r="D117" s="5" t="inlineStr">
+        <is>
+          <t>Ринг Авто</t>
+        </is>
+      </c>
+      <c r="E117" s="5" t="inlineStr">
+        <is>
+          <t>ONLINE ООО "РИНГ С" ВОРОНЕЖ</t>
+        </is>
+      </c>
+      <c r="F117" s="5" t="inlineStr">
+        <is>
+          <t>Валерия Солдатова</t>
+        </is>
+      </c>
+      <c r="G117" s="4" t="inlineStr">
+        <is>
+          <t>09.09.2026</t>
+        </is>
+      </c>
+      <c r="H117" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="I99" s="5" t="inlineStr">
-        <is>
-          <t>Geely</t>
-        </is>
-      </c>
-      <c r="J99" s="5" t="inlineStr">
-        <is>
-          <t>GEELY OKAVANGO</t>
-        </is>
-      </c>
-      <c r="K99" s="5" t="inlineStr">
-        <is>
-          <t>L6TVX1S66TY900885</t>
-        </is>
-      </c>
-      <c r="L99" s="4" t="inlineStr">
-        <is>
-          <t>МП2</t>
-        </is>
-      </c>
-      <c r="M99" s="5" t="inlineStr">
-        <is>
-          <t>Фокин Борис</t>
-        </is>
-      </c>
-      <c r="N99" s="5" t="inlineStr">
-        <is>
-          <t>ПРЕДДКП ОПЛАЧЕН</t>
-        </is>
-      </c>
-      <c r="O99" s="7" t="inlineStr">
-        <is>
-          <t>https://back.sberauto.com/crm/leads/538554</t>
+      <c r="I117" s="5" t="inlineStr">
+        <is>
+          <t>GAC</t>
+        </is>
+      </c>
+      <c r="J117" s="5" t="inlineStr">
+        <is>
+          <t>GS8</t>
+        </is>
+      </c>
+      <c r="K117" s="5" t="inlineStr">
+        <is>
+          <t>LMGJU3G82T1064619</t>
+        </is>
+      </c>
+      <c r="L117" s="4" t="inlineStr">
+        <is>
+          <t>МП2</t>
+        </is>
+      </c>
+      <c r="M117" s="5" t="inlineStr">
+        <is>
+          <t>Фокин Борис</t>
+        </is>
+      </c>
+      <c r="N117" s="5" t="inlineStr">
+        <is>
+          <t>ПРЕДДКП ОПЛАЧЕН</t>
+        </is>
+      </c>
+      <c r="O117" s="7" t="inlineStr">
+        <is>
+          <t>https://back.sberauto.com/crm/leads/552786</t>
         </is>
       </c>
     </row>
@@ -7705,6 +9019,24 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O97" r:id="rId93"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O98" r:id="rId94"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O99" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O100" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O101" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O102" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O103" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O104" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O105" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O106" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O107" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O108" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O109" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O110" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O111" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O112" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O113" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O114" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O115" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O116" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O117" r:id="rId113"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
